--- a/PENDENCIAS_TOTVS_BIOFLOR.xlsx
+++ b/PENDENCIAS_TOTVS_BIOFLOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Controle_NF - 2.0\painel_pendencias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6487C7C-99FF-4B36-8AA9-C85D433B1C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078901DE-9F36-4AB7-A83A-0BA134F45E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C471EACF-5D06-4AC2-B752-69A0BE9168F9}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="valid" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$T$304</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$T$299</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8761" uniqueCount="1414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8666" uniqueCount="1400">
   <si>
     <t>Tipo</t>
   </si>
@@ -3127,48 +3127,6 @@
   </si>
   <si>
     <t>R$ 3.084,00</t>
-  </si>
-  <si>
-    <t>PIACITELLI EMPREENDIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>002582</t>
-  </si>
-  <si>
-    <t>R$ 16.589,95</t>
-  </si>
-  <si>
-    <t>MARCOS AUGUSTO DE CAMPOS</t>
-  </si>
-  <si>
-    <t>002584</t>
-  </si>
-  <si>
-    <t>R$ 17.691,97</t>
-  </si>
-  <si>
-    <t>61.990.670 FABIO JUNIOR GONCALVES</t>
-  </si>
-  <si>
-    <t>002586</t>
-  </si>
-  <si>
-    <t>R$ 11.500,00</t>
-  </si>
-  <si>
-    <t>LUCAS MACEDO FAGUNDES SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
-  </si>
-  <si>
-    <t>R$ 5.817,28</t>
-  </si>
-  <si>
-    <t>OTC SERVICOS ADMINISTRATIVOS E CONSULTORIA LTDA</t>
-  </si>
-  <si>
-    <t>002589</t>
-  </si>
-  <si>
-    <t>R$ 10.686,06</t>
   </si>
   <si>
     <t>CLIMETRO CLINICA MEDICA DO TRABALHO LTDA</t>
@@ -4957,7 +4915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBD8DE6-E0AD-4EC4-ABEF-FC9321AB7545}">
-  <dimension ref="A1:T304"/>
+  <dimension ref="A1:T299"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
@@ -8659,10 +8617,10 @@
         <v>13</v>
       </c>
       <c r="G60" s="38" t="s">
-        <v>121</v>
+        <v>808</v>
       </c>
       <c r="H60" s="38" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I60" s="38" t="s">
         <v>13</v>
@@ -8686,7 +8644,7 @@
         <v>1031</v>
       </c>
       <c r="P60" s="39" t="s">
-        <v>877</v>
+        <v>14</v>
       </c>
       <c r="Q60" s="39" t="s">
         <v>13</v>
@@ -8721,10 +8679,10 @@
         <v>13</v>
       </c>
       <c r="G61" s="38" t="s">
-        <v>121</v>
+        <v>713</v>
       </c>
       <c r="H61" s="38" t="s">
-        <v>138</v>
+        <v>669</v>
       </c>
       <c r="I61" s="38" t="s">
         <v>13</v>
@@ -8748,7 +8706,7 @@
         <v>1034</v>
       </c>
       <c r="P61" s="39" t="s">
-        <v>877</v>
+        <v>14</v>
       </c>
       <c r="Q61" s="39" t="s">
         <v>13</v>
@@ -8764,407 +8722,407 @@
       </c>
     </row>
     <row r="62" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="38" t="s">
-        <v>849</v>
-      </c>
-      <c r="B62" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="39" t="s">
+      <c r="A62" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B62" s="35" t="s">
+        <v>658</v>
+      </c>
+      <c r="C62" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="D62" s="35" t="s">
+        <v>651</v>
+      </c>
+      <c r="E62" s="36" t="s">
+        <v>659</v>
+      </c>
+      <c r="F62" s="37" t="s">
+        <v>660</v>
+      </c>
+      <c r="G62" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="H62" s="35" t="s">
         <v>1035</v>
       </c>
-      <c r="D62" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E62" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" s="38" t="s">
+      <c r="I62" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="K62" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="L62" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="M62" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="N62" s="35" t="s">
+        <v>662</v>
+      </c>
+      <c r="O62" s="37" t="s">
+        <v>660</v>
+      </c>
+      <c r="P62" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q62" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="R62" s="42">
+        <v>46160</v>
+      </c>
+      <c r="S62" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="T62" s="35" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="29" t="s">
+        <v>663</v>
+      </c>
+      <c r="B63" s="29" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C63" s="30" t="s">
+        <v>802</v>
+      </c>
+      <c r="D63" s="29" t="s">
+        <v>653</v>
+      </c>
+      <c r="E63" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="31" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G63" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H63" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="I63" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="J63" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="K63" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="L63" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="M63" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="N63" s="29" t="s">
+        <v>1037</v>
+      </c>
+      <c r="O63" s="31" t="s">
+        <v>1023</v>
+      </c>
+      <c r="P63" s="30" t="s">
+        <v>803</v>
+      </c>
+      <c r="Q63" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="R63" s="47">
+        <v>46183</v>
+      </c>
+      <c r="S63" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="T63" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B64" s="29" t="s">
+        <v>647</v>
+      </c>
+      <c r="C64" s="30" t="s">
+        <v>632</v>
+      </c>
+      <c r="D64" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="E64" s="30" t="s">
+        <v>648</v>
+      </c>
+      <c r="F64" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="G64" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H64" s="29" t="s">
+        <v>1014</v>
+      </c>
+      <c r="I64" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="J64" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="K64" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="L64" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="M64" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="N64" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="O64" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="P64" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q64" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="R64" s="47">
+        <v>46176</v>
+      </c>
+      <c r="S64" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="T64" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B65" s="29" t="s">
+        <v>631</v>
+      </c>
+      <c r="C65" s="30" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D65" s="29" t="s">
+        <v>637</v>
+      </c>
+      <c r="E65" s="30" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F65" s="31" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G65" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="H62" s="38" t="s">
+      <c r="H65" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="I62" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="J62" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="K62" s="38" t="s">
-        <v>852</v>
-      </c>
-      <c r="L62" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="M62" s="38" t="s">
+      <c r="I65" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="N62" s="38" t="s">
-        <v>1036</v>
-      </c>
-      <c r="O62" s="40" t="s">
-        <v>1037</v>
-      </c>
-      <c r="P62" s="39" t="s">
-        <v>877</v>
-      </c>
-      <c r="Q62" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="R62" s="43">
-        <v>46192</v>
-      </c>
-      <c r="S62" s="38" t="s">
-        <v>633</v>
-      </c>
-      <c r="T62" s="38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="38" t="s">
-        <v>849</v>
-      </c>
-      <c r="B63" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="39" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D63" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E63" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="F63" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="G63" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="H63" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="I63" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="J63" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="K63" s="38" t="s">
-        <v>852</v>
-      </c>
-      <c r="L63" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="M63" s="38" t="s">
+      <c r="J65" s="30" t="s">
+        <v>1041</v>
+      </c>
+      <c r="K65" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="L65" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="M65" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="N63" s="38" t="s">
-        <v>890</v>
-      </c>
-      <c r="O63" s="40" t="s">
-        <v>1039</v>
-      </c>
-      <c r="P63" s="39" t="s">
-        <v>877</v>
-      </c>
-      <c r="Q63" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="R63" s="43">
-        <v>46192</v>
-      </c>
-      <c r="S63" s="38" t="s">
-        <v>633</v>
-      </c>
-      <c r="T63" s="38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="38" t="s">
-        <v>849</v>
-      </c>
-      <c r="B64" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="39" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D64" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E64" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="H64" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="I64" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="J64" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="K64" s="38" t="s">
-        <v>852</v>
-      </c>
-      <c r="L64" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="M64" s="38" t="s">
+      <c r="N65" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="O65" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P65" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q65" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="R65" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="S65" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="T65" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B66" s="29" t="s">
+        <v>819</v>
+      </c>
+      <c r="C66" s="30" t="s">
+        <v>820</v>
+      </c>
+      <c r="D66" s="29" t="s">
+        <v>653</v>
+      </c>
+      <c r="E66" s="30" t="s">
+        <v>821</v>
+      </c>
+      <c r="F66" s="31" t="s">
+        <v>822</v>
+      </c>
+      <c r="G66" s="29" t="s">
+        <v>698</v>
+      </c>
+      <c r="H66" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="I66" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="N64" s="38" t="s">
-        <v>1041</v>
-      </c>
-      <c r="O64" s="40" t="s">
-        <v>1042</v>
-      </c>
-      <c r="P64" s="39" t="s">
-        <v>877</v>
-      </c>
-      <c r="Q64" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="R64" s="43">
-        <v>46192</v>
-      </c>
-      <c r="S64" s="38" t="s">
-        <v>633</v>
-      </c>
-      <c r="T64" s="38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="38" t="s">
-        <v>849</v>
-      </c>
-      <c r="B65" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="39" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D65" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="F65" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="G65" s="38" t="s">
-        <v>808</v>
-      </c>
-      <c r="H65" s="38" t="s">
+      <c r="J66" s="30" t="s">
+        <v>823</v>
+      </c>
+      <c r="K66" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="L66" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="M66" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="N66" s="29" t="s">
+        <v>816</v>
+      </c>
+      <c r="O66" s="31" t="s">
+        <v>817</v>
+      </c>
+      <c r="P66" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q66" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="R66" s="47">
+        <v>46193</v>
+      </c>
+      <c r="S66" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="T66" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B67" s="29" t="s">
+        <v>811</v>
+      </c>
+      <c r="C67" s="30" t="s">
+        <v>812</v>
+      </c>
+      <c r="D67" s="29" t="s">
+        <v>653</v>
+      </c>
+      <c r="E67" s="30" t="s">
+        <v>813</v>
+      </c>
+      <c r="F67" s="31" t="s">
+        <v>814</v>
+      </c>
+      <c r="G67" s="29" t="s">
+        <v>698</v>
+      </c>
+      <c r="H67" s="29" t="s">
         <v>145</v>
       </c>
-      <c r="I65" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="J65" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="K65" s="38" t="s">
-        <v>852</v>
-      </c>
-      <c r="L65" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="M65" s="38" t="s">
+      <c r="I67" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="N65" s="38" t="s">
-        <v>1044</v>
-      </c>
-      <c r="O65" s="40" t="s">
-        <v>1045</v>
-      </c>
-      <c r="P65" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q65" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="R65" s="43">
-        <v>46192</v>
-      </c>
-      <c r="S65" s="38" t="s">
-        <v>633</v>
-      </c>
-      <c r="T65" s="38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="38" t="s">
-        <v>849</v>
-      </c>
-      <c r="B66" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="39" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D66" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="38" t="s">
-        <v>713</v>
-      </c>
-      <c r="H66" s="38" t="s">
-        <v>669</v>
-      </c>
-      <c r="I66" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="J66" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="K66" s="38" t="s">
-        <v>852</v>
-      </c>
-      <c r="L66" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="M66" s="38" t="s">
+      <c r="J67" s="30" t="s">
+        <v>815</v>
+      </c>
+      <c r="K67" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="L67" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="M67" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="N66" s="38" t="s">
-        <v>1047</v>
-      </c>
-      <c r="O66" s="40" t="s">
-        <v>1048</v>
-      </c>
-      <c r="P66" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q66" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="R66" s="43">
-        <v>46192</v>
-      </c>
-      <c r="S66" s="38" t="s">
-        <v>633</v>
-      </c>
-      <c r="T66" s="38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="B67" s="35" t="s">
-        <v>658</v>
-      </c>
-      <c r="C67" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="D67" s="35" t="s">
-        <v>651</v>
-      </c>
-      <c r="E67" s="36" t="s">
-        <v>659</v>
-      </c>
-      <c r="F67" s="37" t="s">
-        <v>660</v>
-      </c>
-      <c r="G67" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="H67" s="35" t="s">
-        <v>1049</v>
-      </c>
-      <c r="I67" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="J67" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="K67" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="L67" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="M67" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="N67" s="35" t="s">
-        <v>662</v>
-      </c>
-      <c r="O67" s="37" t="s">
-        <v>660</v>
-      </c>
-      <c r="P67" s="36" t="s">
+      <c r="N67" s="29" t="s">
+        <v>816</v>
+      </c>
+      <c r="O67" s="31" t="s">
+        <v>817</v>
+      </c>
+      <c r="P67" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="Q67" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="R67" s="42">
-        <v>46160</v>
+      <c r="Q67" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="R67" s="47">
+        <v>46193</v>
       </c>
       <c r="S67" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="T67" s="35" t="s">
+      <c r="T67" s="29" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="29" t="s">
-        <v>663</v>
+        <v>20</v>
       </c>
       <c r="B68" s="29" t="s">
-        <v>1050</v>
+        <v>804</v>
       </c>
       <c r="C68" s="30" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="D68" s="29" t="s">
         <v>653</v>
       </c>
       <c r="E68" s="30" t="s">
-        <v>13</v>
+        <v>806</v>
       </c>
       <c r="F68" s="31" t="s">
-        <v>1023</v>
+        <v>807</v>
       </c>
       <c r="G68" s="29" t="s">
-        <v>13</v>
+        <v>808</v>
       </c>
       <c r="H68" s="29" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I68" s="29" t="s">
-        <v>266</v>
+        <v>16</v>
       </c>
       <c r="J68" s="30" t="s">
-        <v>13</v>
+        <v>809</v>
       </c>
       <c r="K68" s="29" t="s">
         <v>21</v>
@@ -9173,28 +9131,28 @@
         <v>13</v>
       </c>
       <c r="M68" s="29" t="s">
-        <v>266</v>
+        <v>16</v>
       </c>
       <c r="N68" s="29" t="s">
-        <v>1051</v>
+        <v>810</v>
       </c>
       <c r="O68" s="31" t="s">
-        <v>1023</v>
+        <v>807</v>
       </c>
       <c r="P68" s="30" t="s">
-        <v>803</v>
+        <v>17</v>
       </c>
       <c r="Q68" s="30" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R68" s="47">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="S68" s="25" t="s">
         <v>15</v>
       </c>
       <c r="T68" s="29" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9202,31 +9160,31 @@
         <v>20</v>
       </c>
       <c r="B69" s="29" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="C69" s="30" t="s">
-        <v>632</v>
+        <v>22</v>
       </c>
       <c r="D69" s="29" t="s">
-        <v>132</v>
+        <v>649</v>
       </c>
       <c r="E69" s="30" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="F69" s="31" t="s">
-        <v>636</v>
+        <v>656</v>
       </c>
       <c r="G69" s="29" t="s">
-        <v>13</v>
+        <v>657</v>
       </c>
       <c r="H69" s="29" t="s">
-        <v>1014</v>
+        <v>730</v>
       </c>
       <c r="I69" s="29" t="s">
         <v>16</v>
       </c>
       <c r="J69" s="30" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="K69" s="29" t="s">
         <v>21</v>
@@ -9238,10 +9196,10 @@
         <v>16</v>
       </c>
       <c r="N69" s="29" t="s">
-        <v>635</v>
+        <v>1061</v>
       </c>
       <c r="O69" s="31" t="s">
-        <v>636</v>
+        <v>13</v>
       </c>
       <c r="P69" s="30" t="s">
         <v>17</v>
@@ -9249,11 +9207,11 @@
       <c r="Q69" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="R69" s="47">
-        <v>46176</v>
-      </c>
-      <c r="S69" s="25" t="s">
-        <v>15</v>
+      <c r="R69" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="S69" s="29" t="s">
+        <v>13</v>
       </c>
       <c r="T69" s="29" t="s">
         <v>30</v>
@@ -9264,31 +9222,31 @@
         <v>20</v>
       </c>
       <c r="B70" s="29" t="s">
-        <v>631</v>
+        <v>674</v>
       </c>
       <c r="C70" s="30" t="s">
-        <v>1052</v>
+        <v>22</v>
       </c>
       <c r="D70" s="29" t="s">
-        <v>637</v>
+        <v>651</v>
       </c>
       <c r="E70" s="30" t="s">
-        <v>1053</v>
+        <v>675</v>
       </c>
       <c r="F70" s="31" t="s">
-        <v>1054</v>
+        <v>676</v>
       </c>
       <c r="G70" s="29" t="s">
-        <v>121</v>
+        <v>665</v>
       </c>
       <c r="H70" s="29" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="I70" s="29" t="s">
         <v>16</v>
       </c>
       <c r="J70" s="30" t="s">
-        <v>1055</v>
+        <v>29</v>
       </c>
       <c r="K70" s="29" t="s">
         <v>21</v>
@@ -9300,22 +9258,22 @@
         <v>16</v>
       </c>
       <c r="N70" s="29" t="s">
-        <v>13</v>
+        <v>677</v>
       </c>
       <c r="O70" s="31" t="s">
-        <v>13</v>
+        <v>678</v>
       </c>
       <c r="P70" s="30" t="s">
         <v>17</v>
       </c>
       <c r="Q70" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="R70" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="S70" s="29" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="R70" s="47">
+        <v>46184</v>
+      </c>
+      <c r="S70" s="25" t="s">
+        <v>15</v>
       </c>
       <c r="T70" s="29" t="s">
         <v>30</v>
@@ -9326,31 +9284,31 @@
         <v>20</v>
       </c>
       <c r="B71" s="29" t="s">
-        <v>819</v>
+        <v>679</v>
       </c>
       <c r="C71" s="30" t="s">
-        <v>820</v>
+        <v>667</v>
       </c>
       <c r="D71" s="29" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E71" s="30" t="s">
-        <v>821</v>
+        <v>680</v>
       </c>
       <c r="F71" s="31" t="s">
-        <v>822</v>
+        <v>681</v>
       </c>
       <c r="G71" s="29" t="s">
-        <v>698</v>
+        <v>665</v>
       </c>
       <c r="H71" s="29" t="s">
-        <v>145</v>
+        <v>245</v>
       </c>
       <c r="I71" s="29" t="s">
         <v>16</v>
       </c>
       <c r="J71" s="30" t="s">
-        <v>823</v>
+        <v>48</v>
       </c>
       <c r="K71" s="29" t="s">
         <v>21</v>
@@ -9362,19 +9320,19 @@
         <v>16</v>
       </c>
       <c r="N71" s="29" t="s">
-        <v>816</v>
+        <v>682</v>
       </c>
       <c r="O71" s="31" t="s">
-        <v>817</v>
+        <v>681</v>
       </c>
       <c r="P71" s="30" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="Q71" s="30" t="s">
         <v>19</v>
       </c>
       <c r="R71" s="47">
-        <v>46193</v>
+        <v>46185</v>
       </c>
       <c r="S71" s="25" t="s">
         <v>15</v>
@@ -9388,31 +9346,31 @@
         <v>20</v>
       </c>
       <c r="B72" s="29" t="s">
-        <v>811</v>
+        <v>824</v>
       </c>
       <c r="C72" s="30" t="s">
-        <v>812</v>
+        <v>825</v>
       </c>
       <c r="D72" s="29" t="s">
         <v>653</v>
       </c>
       <c r="E72" s="30" t="s">
-        <v>813</v>
+        <v>826</v>
       </c>
       <c r="F72" s="31" t="s">
-        <v>814</v>
+        <v>827</v>
       </c>
       <c r="G72" s="29" t="s">
-        <v>698</v>
+        <v>666</v>
       </c>
       <c r="H72" s="29" t="s">
-        <v>145</v>
+        <v>68</v>
       </c>
       <c r="I72" s="29" t="s">
         <v>16</v>
       </c>
       <c r="J72" s="30" t="s">
-        <v>815</v>
+        <v>828</v>
       </c>
       <c r="K72" s="29" t="s">
         <v>21</v>
@@ -9424,22 +9382,22 @@
         <v>16</v>
       </c>
       <c r="N72" s="29" t="s">
-        <v>816</v>
+        <v>13</v>
       </c>
       <c r="O72" s="31" t="s">
-        <v>817</v>
+        <v>13</v>
       </c>
       <c r="P72" s="30" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="Q72" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="R72" s="47">
-        <v>46193</v>
-      </c>
-      <c r="S72" s="25" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="R72" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="S72" s="29" t="s">
+        <v>13</v>
       </c>
       <c r="T72" s="29" t="s">
         <v>30</v>
@@ -9447,34 +9405,34 @@
     </row>
     <row r="73" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="29" t="s">
-        <v>20</v>
+        <v>663</v>
       </c>
       <c r="B73" s="29" t="s">
-        <v>804</v>
+        <v>1042</v>
       </c>
       <c r="C73" s="30" t="s">
-        <v>805</v>
+        <v>18</v>
       </c>
       <c r="D73" s="29" t="s">
-        <v>653</v>
+        <v>712</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>806</v>
+        <v>13</v>
       </c>
       <c r="F73" s="31" t="s">
-        <v>807</v>
+        <v>1043</v>
       </c>
       <c r="G73" s="29" t="s">
-        <v>808</v>
+        <v>13</v>
       </c>
       <c r="H73" s="29" t="s">
-        <v>145</v>
+        <v>38</v>
       </c>
       <c r="I73" s="29" t="s">
         <v>16</v>
       </c>
       <c r="J73" s="30" t="s">
-        <v>809</v>
+        <v>13</v>
       </c>
       <c r="K73" s="29" t="s">
         <v>21</v>
@@ -9486,10 +9444,10 @@
         <v>16</v>
       </c>
       <c r="N73" s="29" t="s">
-        <v>810</v>
+        <v>1044</v>
       </c>
       <c r="O73" s="31" t="s">
-        <v>807</v>
+        <v>1043</v>
       </c>
       <c r="P73" s="30" t="s">
         <v>17</v>
@@ -9498,45 +9456,45 @@
         <v>19</v>
       </c>
       <c r="R73" s="47">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="S73" s="25" t="s">
         <v>15</v>
       </c>
       <c r="T73" s="29" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="29" t="s">
-        <v>20</v>
+        <v>663</v>
       </c>
       <c r="B74" s="29" t="s">
-        <v>654</v>
+        <v>1045</v>
       </c>
       <c r="C74" s="30" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D74" s="29" t="s">
-        <v>649</v>
+        <v>712</v>
       </c>
       <c r="E74" s="30" t="s">
-        <v>655</v>
+        <v>13</v>
       </c>
       <c r="F74" s="31" t="s">
-        <v>656</v>
+        <v>1046</v>
       </c>
       <c r="G74" s="29" t="s">
-        <v>657</v>
+        <v>13</v>
       </c>
       <c r="H74" s="29" t="s">
-        <v>730</v>
+        <v>38</v>
       </c>
       <c r="I74" s="29" t="s">
         <v>16</v>
       </c>
       <c r="J74" s="30" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="K74" s="29" t="s">
         <v>21</v>
@@ -9548,25 +9506,25 @@
         <v>16</v>
       </c>
       <c r="N74" s="29" t="s">
-        <v>1075</v>
+        <v>1047</v>
       </c>
       <c r="O74" s="31" t="s">
-        <v>13</v>
+        <v>1046</v>
       </c>
       <c r="P74" s="30" t="s">
         <v>17</v>
       </c>
       <c r="Q74" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="R74" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="S74" s="29" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="R74" s="47">
+        <v>46191</v>
+      </c>
+      <c r="S74" s="25" t="s">
+        <v>15</v>
       </c>
       <c r="T74" s="29" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9574,31 +9532,31 @@
         <v>20</v>
       </c>
       <c r="B75" s="29" t="s">
-        <v>674</v>
+        <v>836</v>
       </c>
       <c r="C75" s="30" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D75" s="29" t="s">
-        <v>651</v>
+        <v>700</v>
       </c>
       <c r="E75" s="30" t="s">
-        <v>675</v>
+        <v>837</v>
       </c>
       <c r="F75" s="31" t="s">
-        <v>676</v>
+        <v>838</v>
       </c>
       <c r="G75" s="29" t="s">
-        <v>665</v>
+        <v>703</v>
       </c>
       <c r="H75" s="29" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="I75" s="29" t="s">
         <v>16</v>
       </c>
       <c r="J75" s="30" t="s">
-        <v>29</v>
+        <v>839</v>
       </c>
       <c r="K75" s="29" t="s">
         <v>21</v>
@@ -9610,10 +9568,10 @@
         <v>16</v>
       </c>
       <c r="N75" s="29" t="s">
-        <v>677</v>
+        <v>840</v>
       </c>
       <c r="O75" s="31" t="s">
-        <v>678</v>
+        <v>838</v>
       </c>
       <c r="P75" s="30" t="s">
         <v>17</v>
@@ -9622,7 +9580,7 @@
         <v>19</v>
       </c>
       <c r="R75" s="47">
-        <v>46184</v>
+        <v>46193</v>
       </c>
       <c r="S75" s="25" t="s">
         <v>15</v>
@@ -9636,31 +9594,31 @@
         <v>20</v>
       </c>
       <c r="B76" s="29" t="s">
-        <v>679</v>
+        <v>829</v>
       </c>
       <c r="C76" s="30" t="s">
-        <v>667</v>
+        <v>830</v>
       </c>
       <c r="D76" s="29" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>680</v>
+        <v>831</v>
       </c>
       <c r="F76" s="31" t="s">
-        <v>681</v>
+        <v>832</v>
       </c>
       <c r="G76" s="29" t="s">
-        <v>665</v>
+        <v>13</v>
       </c>
       <c r="H76" s="29" t="s">
-        <v>245</v>
+        <v>23</v>
       </c>
       <c r="I76" s="29" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J76" s="30" t="s">
-        <v>48</v>
+        <v>833</v>
       </c>
       <c r="K76" s="29" t="s">
         <v>21</v>
@@ -9669,22 +9627,22 @@
         <v>13</v>
       </c>
       <c r="M76" s="29" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="N76" s="29" t="s">
-        <v>682</v>
+        <v>834</v>
       </c>
       <c r="O76" s="31" t="s">
-        <v>681</v>
+        <v>835</v>
       </c>
       <c r="P76" s="30" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q76" s="30" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="R76" s="47">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="S76" s="25" t="s">
         <v>15</v>
@@ -9698,31 +9656,31 @@
         <v>20</v>
       </c>
       <c r="B77" s="29" t="s">
-        <v>824</v>
+        <v>640</v>
       </c>
       <c r="C77" s="30" t="s">
-        <v>825</v>
+        <v>641</v>
       </c>
       <c r="D77" s="29" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="E77" s="30" t="s">
-        <v>826</v>
+        <v>643</v>
       </c>
       <c r="F77" s="31" t="s">
-        <v>827</v>
+        <v>644</v>
       </c>
       <c r="G77" s="29" t="s">
-        <v>666</v>
+        <v>645</v>
       </c>
       <c r="H77" s="29" t="s">
-        <v>68</v>
+        <v>669</v>
       </c>
       <c r="I77" s="29" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J77" s="30" t="s">
-        <v>828</v>
+        <v>646</v>
       </c>
       <c r="K77" s="29" t="s">
         <v>21</v>
@@ -9731,13 +9689,13 @@
         <v>13</v>
       </c>
       <c r="M77" s="29" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="N77" s="29" t="s">
-        <v>13</v>
+        <v>841</v>
       </c>
       <c r="O77" s="31" t="s">
-        <v>13</v>
+        <v>644</v>
       </c>
       <c r="P77" s="30" t="s">
         <v>17</v>
@@ -9745,11 +9703,11 @@
       <c r="Q77" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="R77" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="S77" s="29" t="s">
-        <v>13</v>
+      <c r="R77" s="47">
+        <v>46190</v>
+      </c>
+      <c r="S77" s="25" t="s">
+        <v>15</v>
       </c>
       <c r="T77" s="29" t="s">
         <v>30</v>
@@ -9757,34 +9715,34 @@
     </row>
     <row r="78" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="29" t="s">
-        <v>663</v>
+        <v>20</v>
       </c>
       <c r="B78" s="29" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="C78" s="30" t="s">
-        <v>18</v>
+        <v>1052</v>
       </c>
       <c r="D78" s="29" t="s">
         <v>712</v>
       </c>
       <c r="E78" s="30" t="s">
-        <v>13</v>
+        <v>1053</v>
       </c>
       <c r="F78" s="31" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="G78" s="29" t="s">
-        <v>13</v>
+        <v>713</v>
       </c>
       <c r="H78" s="29" t="s">
-        <v>38</v>
+        <v>669</v>
       </c>
       <c r="I78" s="29" t="s">
         <v>16</v>
       </c>
       <c r="J78" s="30" t="s">
-        <v>13</v>
+        <v>1055</v>
       </c>
       <c r="K78" s="29" t="s">
         <v>21</v>
@@ -9796,10 +9754,10 @@
         <v>16</v>
       </c>
       <c r="N78" s="29" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="O78" s="31" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="P78" s="30" t="s">
         <v>17</v>
@@ -9808,74 +9766,74 @@
         <v>19</v>
       </c>
       <c r="R78" s="47">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="S78" s="25" t="s">
         <v>15</v>
       </c>
       <c r="T78" s="29" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="79" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="29" t="s">
+      <c r="A79" s="32" t="s">
         <v>663</v>
       </c>
-      <c r="B79" s="29" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C79" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="D79" s="29" t="s">
-        <v>712</v>
-      </c>
-      <c r="E79" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="31" t="s">
-        <v>1060</v>
-      </c>
-      <c r="G79" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="H79" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="I79" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="J79" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="K79" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="L79" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="M79" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="N79" s="29" t="s">
-        <v>1061</v>
-      </c>
-      <c r="O79" s="31" t="s">
-        <v>1060</v>
-      </c>
-      <c r="P79" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q79" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="R79" s="47">
-        <v>46191</v>
-      </c>
-      <c r="S79" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="T79" s="29" t="s">
+      <c r="B79" s="32" t="s">
+        <v>695</v>
+      </c>
+      <c r="C79" s="33" t="s">
+        <v>664</v>
+      </c>
+      <c r="D79" s="32" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E79" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" s="34" t="s">
+        <v>696</v>
+      </c>
+      <c r="G79" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H79" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="I79" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="J79" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="K79" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L79" s="32" t="s">
+        <v>1398</v>
+      </c>
+      <c r="M79" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="N79" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="O79" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="P79" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q79" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="R79" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="S79" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="T79" s="32" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9884,31 +9842,31 @@
         <v>20</v>
       </c>
       <c r="B80" s="29" t="s">
-        <v>836</v>
+        <v>670</v>
       </c>
       <c r="C80" s="30" t="s">
-        <v>18</v>
+        <v>671</v>
       </c>
       <c r="D80" s="29" t="s">
-        <v>700</v>
+        <v>651</v>
       </c>
       <c r="E80" s="30" t="s">
-        <v>837</v>
+        <v>672</v>
       </c>
       <c r="F80" s="31" t="s">
-        <v>838</v>
+        <v>673</v>
       </c>
       <c r="G80" s="29" t="s">
-        <v>703</v>
+        <v>665</v>
       </c>
       <c r="H80" s="29" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="I80" s="29" t="s">
         <v>16</v>
       </c>
       <c r="J80" s="30" t="s">
-        <v>839</v>
+        <v>111</v>
       </c>
       <c r="K80" s="29" t="s">
         <v>21</v>
@@ -9920,10 +9878,10 @@
         <v>16</v>
       </c>
       <c r="N80" s="29" t="s">
-        <v>840</v>
+        <v>13</v>
       </c>
       <c r="O80" s="31" t="s">
-        <v>838</v>
+        <v>13</v>
       </c>
       <c r="P80" s="30" t="s">
         <v>17</v>
@@ -9931,200 +9889,200 @@
       <c r="Q80" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="R80" s="47">
-        <v>46193</v>
-      </c>
-      <c r="S80" s="25" t="s">
-        <v>15</v>
+      <c r="R80" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="S80" s="29" t="s">
+        <v>13</v>
       </c>
       <c r="T80" s="29" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="81" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B81" s="29" t="s">
-        <v>829</v>
-      </c>
-      <c r="C81" s="30" t="s">
-        <v>830</v>
-      </c>
-      <c r="D81" s="29" t="s">
-        <v>653</v>
-      </c>
-      <c r="E81" s="30" t="s">
-        <v>831</v>
-      </c>
-      <c r="F81" s="31" t="s">
-        <v>832</v>
-      </c>
-      <c r="G81" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="H81" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="I81" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="J81" s="30" t="s">
-        <v>833</v>
-      </c>
-      <c r="K81" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="L81" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="M81" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="N81" s="29" t="s">
-        <v>834</v>
-      </c>
-      <c r="O81" s="31" t="s">
-        <v>835</v>
-      </c>
-      <c r="P81" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q81" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="R81" s="47">
-        <v>46188</v>
-      </c>
-      <c r="S81" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="T81" s="29" t="s">
-        <v>30</v>
+      <c r="A81" s="32" t="s">
+        <v>663</v>
+      </c>
+      <c r="B81" s="32" t="s">
+        <v>932</v>
+      </c>
+      <c r="C81" s="33" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D81" s="32" t="s">
+        <v>652</v>
+      </c>
+      <c r="E81" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" s="34" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G81" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H81" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="I81" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="K81" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L81" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="M81" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="N81" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="O81" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="P81" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q81" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="R81" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="S81" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="T81" s="32" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="82" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B82" s="29" t="s">
-        <v>640</v>
-      </c>
-      <c r="C82" s="30" t="s">
-        <v>641</v>
-      </c>
-      <c r="D82" s="29" t="s">
-        <v>642</v>
-      </c>
-      <c r="E82" s="30" t="s">
-        <v>643</v>
-      </c>
-      <c r="F82" s="31" t="s">
-        <v>644</v>
-      </c>
-      <c r="G82" s="29" t="s">
-        <v>645</v>
-      </c>
-      <c r="H82" s="29" t="s">
-        <v>669</v>
-      </c>
-      <c r="I82" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="J82" s="30" t="s">
-        <v>646</v>
-      </c>
-      <c r="K82" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="L82" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="M82" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="N82" s="29" t="s">
-        <v>841</v>
-      </c>
-      <c r="O82" s="31" t="s">
-        <v>644</v>
-      </c>
-      <c r="P82" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q82" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="R82" s="47">
-        <v>46190</v>
-      </c>
-      <c r="S82" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="T82" s="29" t="s">
-        <v>30</v>
+      <c r="A82" s="32" t="s">
+        <v>663</v>
+      </c>
+      <c r="B82" s="32" t="s">
+        <v>723</v>
+      </c>
+      <c r="C82" s="33" t="s">
+        <v>724</v>
+      </c>
+      <c r="D82" s="32" t="s">
+        <v>652</v>
+      </c>
+      <c r="E82" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="34" t="s">
+        <v>725</v>
+      </c>
+      <c r="G82" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H82" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="I82" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="J82" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="K82" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L82" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="M82" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="N82" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="O82" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="P82" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q82" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="R82" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="S82" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="T82" s="32" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B83" s="29" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C83" s="30" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D83" s="29" t="s">
-        <v>712</v>
-      </c>
-      <c r="E83" s="30" t="s">
-        <v>1067</v>
-      </c>
-      <c r="F83" s="31" t="s">
-        <v>1068</v>
-      </c>
-      <c r="G83" s="29" t="s">
-        <v>713</v>
-      </c>
-      <c r="H83" s="29" t="s">
-        <v>669</v>
-      </c>
-      <c r="I83" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="J83" s="30" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K83" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="L83" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="M83" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="N83" s="29" t="s">
-        <v>1070</v>
-      </c>
-      <c r="O83" s="31" t="s">
-        <v>1068</v>
-      </c>
-      <c r="P83" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q83" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="R83" s="47">
-        <v>46190</v>
-      </c>
-      <c r="S83" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="T83" s="29" t="s">
-        <v>30</v>
+      <c r="A83" s="32" t="s">
+        <v>663</v>
+      </c>
+      <c r="B83" s="32" t="s">
+        <v>726</v>
+      </c>
+      <c r="C83" s="33" t="s">
+        <v>724</v>
+      </c>
+      <c r="D83" s="32" t="s">
+        <v>652</v>
+      </c>
+      <c r="E83" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="34" t="s">
+        <v>727</v>
+      </c>
+      <c r="G83" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H83" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="I83" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="J83" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="K83" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L83" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="M83" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="N83" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="O83" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="P83" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q83" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="R83" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="S83" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="T83" s="32" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="84" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10132,19 +10090,19 @@
         <v>663</v>
       </c>
       <c r="B84" s="32" t="s">
-        <v>695</v>
+        <v>138</v>
       </c>
       <c r="C84" s="33" t="s">
-        <v>664</v>
+        <v>728</v>
       </c>
       <c r="D84" s="32" t="s">
-        <v>1015</v>
+        <v>652</v>
       </c>
       <c r="E84" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F84" s="34" t="s">
-        <v>696</v>
+        <v>729</v>
       </c>
       <c r="G84" s="32" t="s">
         <v>13</v>
@@ -10153,7 +10111,7 @@
         <v>13</v>
       </c>
       <c r="I84" s="32" t="s">
-        <v>266</v>
+        <v>13</v>
       </c>
       <c r="J84" s="33" t="s">
         <v>13</v>
@@ -10162,10 +10120,10 @@
         <v>21</v>
       </c>
       <c r="L84" s="32" t="s">
-        <v>1412</v>
+        <v>13</v>
       </c>
       <c r="M84" s="32" t="s">
-        <v>266</v>
+        <v>13</v>
       </c>
       <c r="N84" s="32" t="s">
         <v>13</v>
@@ -10174,7 +10132,7 @@
         <v>13</v>
       </c>
       <c r="P84" s="33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q84" s="33" t="s">
         <v>13</v>
@@ -10190,65 +10148,65 @@
       </c>
     </row>
     <row r="85" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B85" s="29" t="s">
-        <v>670</v>
-      </c>
-      <c r="C85" s="30" t="s">
-        <v>671</v>
-      </c>
-      <c r="D85" s="29" t="s">
-        <v>651</v>
-      </c>
-      <c r="E85" s="30" t="s">
-        <v>672</v>
-      </c>
-      <c r="F85" s="31" t="s">
+      <c r="A85" s="32" t="s">
+        <v>663</v>
+      </c>
+      <c r="B85" s="32" t="s">
+        <v>730</v>
+      </c>
+      <c r="C85" s="33" t="s">
+        <v>731</v>
+      </c>
+      <c r="D85" s="32" t="s">
+        <v>652</v>
+      </c>
+      <c r="E85" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" s="34" t="s">
         <v>673</v>
       </c>
-      <c r="G85" s="29" t="s">
-        <v>665</v>
-      </c>
-      <c r="H85" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="I85" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="J85" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="K85" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="L85" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="M85" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="N85" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="O85" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="P85" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q85" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="R85" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="S85" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="T85" s="29" t="s">
-        <v>30</v>
+      <c r="G85" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H85" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="I85" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="J85" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="K85" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L85" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="M85" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="N85" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="O85" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="P85" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q85" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="R85" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="S85" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="T85" s="32" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="86" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10256,10 +10214,10 @@
         <v>663</v>
       </c>
       <c r="B86" s="32" t="s">
-        <v>932</v>
+        <v>740</v>
       </c>
       <c r="C86" s="33" t="s">
-        <v>1080</v>
+        <v>741</v>
       </c>
       <c r="D86" s="32" t="s">
         <v>652</v>
@@ -10268,7 +10226,7 @@
         <v>13</v>
       </c>
       <c r="F86" s="34" t="s">
-        <v>1081</v>
+        <v>742</v>
       </c>
       <c r="G86" s="32" t="s">
         <v>13</v>
@@ -10318,10 +10276,10 @@
         <v>663</v>
       </c>
       <c r="B87" s="32" t="s">
-        <v>723</v>
+        <v>743</v>
       </c>
       <c r="C87" s="33" t="s">
-        <v>724</v>
+        <v>741</v>
       </c>
       <c r="D87" s="32" t="s">
         <v>652</v>
@@ -10330,7 +10288,7 @@
         <v>13</v>
       </c>
       <c r="F87" s="34" t="s">
-        <v>725</v>
+        <v>744</v>
       </c>
       <c r="G87" s="32" t="s">
         <v>13</v>
@@ -10380,10 +10338,10 @@
         <v>663</v>
       </c>
       <c r="B88" s="32" t="s">
-        <v>726</v>
+        <v>737</v>
       </c>
       <c r="C88" s="33" t="s">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="D88" s="32" t="s">
         <v>652</v>
@@ -10392,7 +10350,7 @@
         <v>13</v>
       </c>
       <c r="F88" s="34" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
       <c r="G88" s="32" t="s">
         <v>13</v>
@@ -10442,10 +10400,10 @@
         <v>663</v>
       </c>
       <c r="B89" s="32" t="s">
-        <v>138</v>
+        <v>1205</v>
       </c>
       <c r="C89" s="33" t="s">
-        <v>728</v>
+        <v>1206</v>
       </c>
       <c r="D89" s="32" t="s">
         <v>652</v>
@@ -10454,7 +10412,7 @@
         <v>13</v>
       </c>
       <c r="F89" s="34" t="s">
-        <v>729</v>
+        <v>1183</v>
       </c>
       <c r="G89" s="32" t="s">
         <v>13</v>
@@ -10504,10 +10462,10 @@
         <v>663</v>
       </c>
       <c r="B90" s="32" t="s">
-        <v>730</v>
+        <v>1165</v>
       </c>
       <c r="C90" s="33" t="s">
-        <v>731</v>
+        <v>1206</v>
       </c>
       <c r="D90" s="32" t="s">
         <v>652</v>
@@ -10516,7 +10474,7 @@
         <v>13</v>
       </c>
       <c r="F90" s="34" t="s">
-        <v>673</v>
+        <v>1183</v>
       </c>
       <c r="G90" s="32" t="s">
         <v>13</v>
@@ -10566,10 +10524,10 @@
         <v>663</v>
       </c>
       <c r="B91" s="32" t="s">
-        <v>740</v>
+        <v>750</v>
       </c>
       <c r="C91" s="33" t="s">
-        <v>741</v>
+        <v>751</v>
       </c>
       <c r="D91" s="32" t="s">
         <v>652</v>
@@ -10578,7 +10536,7 @@
         <v>13</v>
       </c>
       <c r="F91" s="34" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="G91" s="32" t="s">
         <v>13</v>
@@ -10628,10 +10586,10 @@
         <v>663</v>
       </c>
       <c r="B92" s="32" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="C92" s="33" t="s">
-        <v>741</v>
+        <v>756</v>
       </c>
       <c r="D92" s="32" t="s">
         <v>652</v>
@@ -10640,7 +10598,7 @@
         <v>13</v>
       </c>
       <c r="F92" s="34" t="s">
-        <v>744</v>
+        <v>757</v>
       </c>
       <c r="G92" s="32" t="s">
         <v>13</v>
@@ -10690,10 +10648,10 @@
         <v>663</v>
       </c>
       <c r="B93" s="32" t="s">
-        <v>737</v>
+        <v>758</v>
       </c>
       <c r="C93" s="33" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
       <c r="D93" s="32" t="s">
         <v>652</v>
@@ -10702,7 +10660,7 @@
         <v>13</v>
       </c>
       <c r="F93" s="34" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="G93" s="32" t="s">
         <v>13</v>
@@ -10752,10 +10710,10 @@
         <v>663</v>
       </c>
       <c r="B94" s="32" t="s">
-        <v>1219</v>
+        <v>71</v>
       </c>
       <c r="C94" s="33" t="s">
-        <v>1220</v>
+        <v>761</v>
       </c>
       <c r="D94" s="32" t="s">
         <v>652</v>
@@ -10764,7 +10722,7 @@
         <v>13</v>
       </c>
       <c r="F94" s="34" t="s">
-        <v>1197</v>
+        <v>762</v>
       </c>
       <c r="G94" s="32" t="s">
         <v>13</v>
@@ -10814,10 +10772,10 @@
         <v>663</v>
       </c>
       <c r="B95" s="32" t="s">
-        <v>1179</v>
+        <v>245</v>
       </c>
       <c r="C95" s="33" t="s">
-        <v>1220</v>
+        <v>761</v>
       </c>
       <c r="D95" s="32" t="s">
         <v>652</v>
@@ -10826,7 +10784,7 @@
         <v>13</v>
       </c>
       <c r="F95" s="34" t="s">
-        <v>1197</v>
+        <v>762</v>
       </c>
       <c r="G95" s="32" t="s">
         <v>13</v>
@@ -10876,10 +10834,10 @@
         <v>663</v>
       </c>
       <c r="B96" s="32" t="s">
-        <v>750</v>
+        <v>661</v>
       </c>
       <c r="C96" s="33" t="s">
-        <v>751</v>
+        <v>1259</v>
       </c>
       <c r="D96" s="32" t="s">
         <v>652</v>
@@ -10888,7 +10846,7 @@
         <v>13</v>
       </c>
       <c r="F96" s="34" t="s">
-        <v>735</v>
+        <v>1260</v>
       </c>
       <c r="G96" s="32" t="s">
         <v>13</v>
@@ -10938,10 +10896,10 @@
         <v>663</v>
       </c>
       <c r="B97" s="32" t="s">
-        <v>755</v>
+        <v>764</v>
       </c>
       <c r="C97" s="33" t="s">
-        <v>756</v>
+        <v>765</v>
       </c>
       <c r="D97" s="32" t="s">
         <v>652</v>
@@ -10950,7 +10908,7 @@
         <v>13</v>
       </c>
       <c r="F97" s="34" t="s">
-        <v>757</v>
+        <v>766</v>
       </c>
       <c r="G97" s="32" t="s">
         <v>13</v>
@@ -11000,10 +10958,10 @@
         <v>663</v>
       </c>
       <c r="B98" s="32" t="s">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="C98" s="33" t="s">
-        <v>759</v>
+        <v>768</v>
       </c>
       <c r="D98" s="32" t="s">
         <v>652</v>
@@ -11012,7 +10970,7 @@
         <v>13</v>
       </c>
       <c r="F98" s="34" t="s">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="G98" s="32" t="s">
         <v>13</v>
@@ -11062,19 +11020,19 @@
         <v>663</v>
       </c>
       <c r="B99" s="32" t="s">
-        <v>71</v>
+        <v>687</v>
       </c>
       <c r="C99" s="33" t="s">
-        <v>761</v>
+        <v>688</v>
       </c>
       <c r="D99" s="32" t="s">
-        <v>652</v>
+        <v>637</v>
       </c>
       <c r="E99" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F99" s="34" t="s">
-        <v>762</v>
+        <v>689</v>
       </c>
       <c r="G99" s="32" t="s">
         <v>13</v>
@@ -11083,7 +11041,7 @@
         <v>13</v>
       </c>
       <c r="I99" s="32" t="s">
-        <v>13</v>
+        <v>266</v>
       </c>
       <c r="J99" s="33" t="s">
         <v>13</v>
@@ -11095,7 +11053,7 @@
         <v>13</v>
       </c>
       <c r="M99" s="32" t="s">
-        <v>13</v>
+        <v>266</v>
       </c>
       <c r="N99" s="32" t="s">
         <v>13</v>
@@ -11104,7 +11062,7 @@
         <v>13</v>
       </c>
       <c r="P99" s="33" t="s">
-        <v>13</v>
+        <v>877</v>
       </c>
       <c r="Q99" s="33" t="s">
         <v>13</v>
@@ -11124,10 +11082,10 @@
         <v>663</v>
       </c>
       <c r="B100" s="32" t="s">
-        <v>245</v>
+        <v>845</v>
       </c>
       <c r="C100" s="33" t="s">
-        <v>761</v>
+        <v>688</v>
       </c>
       <c r="D100" s="32" t="s">
         <v>652</v>
@@ -11136,7 +11094,7 @@
         <v>13</v>
       </c>
       <c r="F100" s="34" t="s">
-        <v>762</v>
+        <v>846</v>
       </c>
       <c r="G100" s="32" t="s">
         <v>13</v>
@@ -11166,7 +11124,7 @@
         <v>13</v>
       </c>
       <c r="P100" s="33" t="s">
-        <v>13</v>
+        <v>877</v>
       </c>
       <c r="Q100" s="33" t="s">
         <v>13</v>
@@ -11186,10 +11144,10 @@
         <v>663</v>
       </c>
       <c r="B101" s="32" t="s">
-        <v>661</v>
+        <v>690</v>
       </c>
       <c r="C101" s="33" t="s">
-        <v>1273</v>
+        <v>688</v>
       </c>
       <c r="D101" s="32" t="s">
         <v>652</v>
@@ -11198,7 +11156,7 @@
         <v>13</v>
       </c>
       <c r="F101" s="34" t="s">
-        <v>1274</v>
+        <v>691</v>
       </c>
       <c r="G101" s="32" t="s">
         <v>13</v>
@@ -11228,7 +11186,7 @@
         <v>13</v>
       </c>
       <c r="P101" s="33" t="s">
-        <v>13</v>
+        <v>877</v>
       </c>
       <c r="Q101" s="33" t="s">
         <v>13</v>
@@ -11248,10 +11206,10 @@
         <v>663</v>
       </c>
       <c r="B102" s="32" t="s">
-        <v>764</v>
+        <v>692</v>
       </c>
       <c r="C102" s="33" t="s">
-        <v>765</v>
+        <v>688</v>
       </c>
       <c r="D102" s="32" t="s">
         <v>652</v>
@@ -11260,7 +11218,7 @@
         <v>13</v>
       </c>
       <c r="F102" s="34" t="s">
-        <v>766</v>
+        <v>693</v>
       </c>
       <c r="G102" s="32" t="s">
         <v>13</v>
@@ -11290,7 +11248,7 @@
         <v>13</v>
       </c>
       <c r="P102" s="33" t="s">
-        <v>13</v>
+        <v>877</v>
       </c>
       <c r="Q102" s="33" t="s">
         <v>13</v>
@@ -11310,7 +11268,7 @@
         <v>663</v>
       </c>
       <c r="B103" s="32" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C103" s="33" t="s">
         <v>768</v>
@@ -11322,7 +11280,7 @@
         <v>13</v>
       </c>
       <c r="F103" s="34" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="G103" s="32" t="s">
         <v>13</v>
@@ -11372,19 +11330,19 @@
         <v>663</v>
       </c>
       <c r="B104" s="32" t="s">
-        <v>687</v>
+        <v>772</v>
       </c>
       <c r="C104" s="33" t="s">
-        <v>688</v>
+        <v>773</v>
       </c>
       <c r="D104" s="32" t="s">
-        <v>637</v>
+        <v>652</v>
       </c>
       <c r="E104" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F104" s="34" t="s">
-        <v>689</v>
+        <v>774</v>
       </c>
       <c r="G104" s="32" t="s">
         <v>13</v>
@@ -11393,7 +11351,7 @@
         <v>13</v>
       </c>
       <c r="I104" s="32" t="s">
-        <v>266</v>
+        <v>13</v>
       </c>
       <c r="J104" s="33" t="s">
         <v>13</v>
@@ -11405,7 +11363,7 @@
         <v>13</v>
       </c>
       <c r="M104" s="32" t="s">
-        <v>266</v>
+        <v>13</v>
       </c>
       <c r="N104" s="32" t="s">
         <v>13</v>
@@ -11414,7 +11372,7 @@
         <v>13</v>
       </c>
       <c r="P104" s="33" t="s">
-        <v>877</v>
+        <v>13</v>
       </c>
       <c r="Q104" s="33" t="s">
         <v>13</v>
@@ -11434,10 +11392,10 @@
         <v>663</v>
       </c>
       <c r="B105" s="32" t="s">
-        <v>845</v>
+        <v>775</v>
       </c>
       <c r="C105" s="33" t="s">
-        <v>688</v>
+        <v>776</v>
       </c>
       <c r="D105" s="32" t="s">
         <v>652</v>
@@ -11446,7 +11404,7 @@
         <v>13</v>
       </c>
       <c r="F105" s="34" t="s">
-        <v>846</v>
+        <v>752</v>
       </c>
       <c r="G105" s="32" t="s">
         <v>13</v>
@@ -11476,7 +11434,7 @@
         <v>13</v>
       </c>
       <c r="P105" s="33" t="s">
-        <v>877</v>
+        <v>13</v>
       </c>
       <c r="Q105" s="33" t="s">
         <v>13</v>
@@ -11496,10 +11454,10 @@
         <v>663</v>
       </c>
       <c r="B106" s="32" t="s">
-        <v>690</v>
+        <v>777</v>
       </c>
       <c r="C106" s="33" t="s">
-        <v>688</v>
+        <v>778</v>
       </c>
       <c r="D106" s="32" t="s">
         <v>652</v>
@@ -11508,7 +11466,7 @@
         <v>13</v>
       </c>
       <c r="F106" s="34" t="s">
-        <v>691</v>
+        <v>779</v>
       </c>
       <c r="G106" s="32" t="s">
         <v>13</v>
@@ -11538,7 +11496,7 @@
         <v>13</v>
       </c>
       <c r="P106" s="33" t="s">
-        <v>877</v>
+        <v>13</v>
       </c>
       <c r="Q106" s="33" t="s">
         <v>13</v>
@@ -11558,10 +11516,10 @@
         <v>663</v>
       </c>
       <c r="B107" s="32" t="s">
-        <v>692</v>
+        <v>780</v>
       </c>
       <c r="C107" s="33" t="s">
-        <v>688</v>
+        <v>778</v>
       </c>
       <c r="D107" s="32" t="s">
         <v>652</v>
@@ -11570,7 +11528,7 @@
         <v>13</v>
       </c>
       <c r="F107" s="34" t="s">
-        <v>693</v>
+        <v>781</v>
       </c>
       <c r="G107" s="32" t="s">
         <v>13</v>
@@ -11600,7 +11558,7 @@
         <v>13</v>
       </c>
       <c r="P107" s="33" t="s">
-        <v>877</v>
+        <v>13</v>
       </c>
       <c r="Q107" s="33" t="s">
         <v>13</v>
@@ -11620,10 +11578,10 @@
         <v>663</v>
       </c>
       <c r="B108" s="32" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
       <c r="C108" s="33" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="D108" s="32" t="s">
         <v>652</v>
@@ -11632,7 +11590,7 @@
         <v>13</v>
       </c>
       <c r="F108" s="34" t="s">
-        <v>771</v>
+        <v>784</v>
       </c>
       <c r="G108" s="32" t="s">
         <v>13</v>
@@ -11682,10 +11640,10 @@
         <v>663</v>
       </c>
       <c r="B109" s="32" t="s">
-        <v>772</v>
+        <v>138</v>
       </c>
       <c r="C109" s="33" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
       <c r="D109" s="32" t="s">
         <v>652</v>
@@ -11694,7 +11652,7 @@
         <v>13</v>
       </c>
       <c r="F109" s="34" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
       <c r="G109" s="32" t="s">
         <v>13</v>
@@ -11744,10 +11702,10 @@
         <v>663</v>
       </c>
       <c r="B110" s="32" t="s">
-        <v>775</v>
+        <v>788</v>
       </c>
       <c r="C110" s="33" t="s">
-        <v>776</v>
+        <v>787</v>
       </c>
       <c r="D110" s="32" t="s">
         <v>652</v>
@@ -11756,7 +11714,7 @@
         <v>13</v>
       </c>
       <c r="F110" s="34" t="s">
-        <v>752</v>
+        <v>789</v>
       </c>
       <c r="G110" s="32" t="s">
         <v>13</v>
@@ -11806,10 +11764,10 @@
         <v>663</v>
       </c>
       <c r="B111" s="32" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="C111" s="33" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
       <c r="D111" s="32" t="s">
         <v>652</v>
@@ -11818,7 +11776,7 @@
         <v>13</v>
       </c>
       <c r="F111" s="34" t="s">
-        <v>779</v>
+        <v>793</v>
       </c>
       <c r="G111" s="32" t="s">
         <v>13</v>
@@ -11868,10 +11826,10 @@
         <v>663</v>
       </c>
       <c r="B112" s="32" t="s">
-        <v>780</v>
+        <v>794</v>
       </c>
       <c r="C112" s="33" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
       <c r="D112" s="32" t="s">
         <v>652</v>
@@ -11880,7 +11838,7 @@
         <v>13</v>
       </c>
       <c r="F112" s="34" t="s">
-        <v>781</v>
+        <v>795</v>
       </c>
       <c r="G112" s="32" t="s">
         <v>13</v>
@@ -11930,10 +11888,10 @@
         <v>663</v>
       </c>
       <c r="B113" s="32" t="s">
-        <v>782</v>
+        <v>796</v>
       </c>
       <c r="C113" s="33" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="D113" s="32" t="s">
         <v>652</v>
@@ -11942,7 +11900,7 @@
         <v>13</v>
       </c>
       <c r="F113" s="34" t="s">
-        <v>784</v>
+        <v>797</v>
       </c>
       <c r="G113" s="32" t="s">
         <v>13</v>
@@ -11992,10 +11950,10 @@
         <v>663</v>
       </c>
       <c r="B114" s="32" t="s">
-        <v>138</v>
+        <v>798</v>
       </c>
       <c r="C114" s="33" t="s">
-        <v>785</v>
+        <v>799</v>
       </c>
       <c r="D114" s="32" t="s">
         <v>652</v>
@@ -12004,7 +11962,7 @@
         <v>13</v>
       </c>
       <c r="F114" s="34" t="s">
-        <v>786</v>
+        <v>800</v>
       </c>
       <c r="G114" s="32" t="s">
         <v>13</v>
@@ -12051,22 +12009,22 @@
     </row>
     <row r="115" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="32" t="s">
-        <v>663</v>
+        <v>20</v>
       </c>
       <c r="B115" s="32" t="s">
-        <v>788</v>
+        <v>1391</v>
       </c>
       <c r="C115" s="33" t="s">
-        <v>787</v>
+        <v>1392</v>
       </c>
       <c r="D115" s="32" t="s">
         <v>652</v>
       </c>
       <c r="E115" s="33" t="s">
-        <v>13</v>
+        <v>1393</v>
       </c>
       <c r="F115" s="34" t="s">
-        <v>789</v>
+        <v>1394</v>
       </c>
       <c r="G115" s="32" t="s">
         <v>13</v>
@@ -12075,10 +12033,10 @@
         <v>13</v>
       </c>
       <c r="I115" s="32" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J115" s="33" t="s">
-        <v>13</v>
+        <v>1395</v>
       </c>
       <c r="K115" s="32" t="s">
         <v>21</v>
@@ -12087,7 +12045,7 @@
         <v>13</v>
       </c>
       <c r="M115" s="32" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N115" s="32" t="s">
         <v>13</v>
@@ -12108,7 +12066,7 @@
         <v>13</v>
       </c>
       <c r="T115" s="32" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="116" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12116,19 +12074,19 @@
         <v>663</v>
       </c>
       <c r="B116" s="32" t="s">
-        <v>792</v>
+        <v>732</v>
       </c>
       <c r="C116" s="33" t="s">
-        <v>790</v>
+        <v>733</v>
       </c>
       <c r="D116" s="32" t="s">
-        <v>652</v>
+        <v>58</v>
       </c>
       <c r="E116" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F116" s="34" t="s">
-        <v>793</v>
+        <v>734</v>
       </c>
       <c r="G116" s="32" t="s">
         <v>13</v>
@@ -12137,7 +12095,7 @@
         <v>13</v>
       </c>
       <c r="I116" s="32" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J116" s="33" t="s">
         <v>13</v>
@@ -12149,7 +12107,7 @@
         <v>13</v>
       </c>
       <c r="M116" s="32" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N116" s="32" t="s">
         <v>13</v>
@@ -12178,19 +12136,19 @@
         <v>663</v>
       </c>
       <c r="B117" s="32" t="s">
-        <v>794</v>
+        <v>1068</v>
       </c>
       <c r="C117" s="33" t="s">
-        <v>790</v>
+        <v>1069</v>
       </c>
       <c r="D117" s="32" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E117" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F117" s="34" t="s">
-        <v>795</v>
+        <v>1070</v>
       </c>
       <c r="G117" s="32" t="s">
         <v>13</v>
@@ -12240,19 +12198,19 @@
         <v>663</v>
       </c>
       <c r="B118" s="32" t="s">
-        <v>796</v>
+        <v>1071</v>
       </c>
       <c r="C118" s="33" t="s">
-        <v>790</v>
+        <v>1069</v>
       </c>
       <c r="D118" s="32" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E118" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F118" s="34" t="s">
-        <v>797</v>
+        <v>1070</v>
       </c>
       <c r="G118" s="32" t="s">
         <v>13</v>
@@ -12302,19 +12260,19 @@
         <v>663</v>
       </c>
       <c r="B119" s="32" t="s">
-        <v>798</v>
+        <v>1093</v>
       </c>
       <c r="C119" s="33" t="s">
-        <v>799</v>
+        <v>1094</v>
       </c>
       <c r="D119" s="32" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E119" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F119" s="34" t="s">
-        <v>800</v>
+        <v>1095</v>
       </c>
       <c r="G119" s="32" t="s">
         <v>13</v>
@@ -12361,22 +12319,22 @@
     </row>
     <row r="120" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="32" t="s">
-        <v>20</v>
+        <v>663</v>
       </c>
       <c r="B120" s="32" t="s">
-        <v>1405</v>
+        <v>1096</v>
       </c>
       <c r="C120" s="33" t="s">
-        <v>1406</v>
+        <v>1094</v>
       </c>
       <c r="D120" s="32" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E120" s="33" t="s">
-        <v>1407</v>
+        <v>13</v>
       </c>
       <c r="F120" s="34" t="s">
-        <v>1408</v>
+        <v>1095</v>
       </c>
       <c r="G120" s="32" t="s">
         <v>13</v>
@@ -12385,10 +12343,10 @@
         <v>13</v>
       </c>
       <c r="I120" s="32" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J120" s="33" t="s">
-        <v>1409</v>
+        <v>13</v>
       </c>
       <c r="K120" s="32" t="s">
         <v>21</v>
@@ -12397,7 +12355,7 @@
         <v>13</v>
       </c>
       <c r="M120" s="32" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N120" s="32" t="s">
         <v>13</v>
@@ -12418,7 +12376,7 @@
         <v>13</v>
       </c>
       <c r="T120" s="32" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="121" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12426,19 +12384,19 @@
         <v>663</v>
       </c>
       <c r="B121" s="32" t="s">
-        <v>732</v>
+        <v>1100</v>
       </c>
       <c r="C121" s="33" t="s">
-        <v>733</v>
+        <v>1101</v>
       </c>
       <c r="D121" s="32" t="s">
-        <v>58</v>
+        <v>653</v>
       </c>
       <c r="E121" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F121" s="34" t="s">
-        <v>734</v>
+        <v>1102</v>
       </c>
       <c r="G121" s="32" t="s">
         <v>13</v>
@@ -12447,7 +12405,7 @@
         <v>13</v>
       </c>
       <c r="I121" s="32" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J121" s="33" t="s">
         <v>13</v>
@@ -12459,7 +12417,7 @@
         <v>13</v>
       </c>
       <c r="M121" s="32" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N121" s="32" t="s">
         <v>13</v>
@@ -12488,10 +12446,10 @@
         <v>663</v>
       </c>
       <c r="B122" s="32" t="s">
-        <v>1082</v>
+        <v>1103</v>
       </c>
       <c r="C122" s="33" t="s">
-        <v>1083</v>
+        <v>1101</v>
       </c>
       <c r="D122" s="32" t="s">
         <v>653</v>
@@ -12500,7 +12458,7 @@
         <v>13</v>
       </c>
       <c r="F122" s="34" t="s">
-        <v>1084</v>
+        <v>1102</v>
       </c>
       <c r="G122" s="32" t="s">
         <v>13</v>
@@ -12550,10 +12508,10 @@
         <v>663</v>
       </c>
       <c r="B123" s="32" t="s">
-        <v>1085</v>
+        <v>1126</v>
       </c>
       <c r="C123" s="33" t="s">
-        <v>1083</v>
+        <v>1127</v>
       </c>
       <c r="D123" s="32" t="s">
         <v>653</v>
@@ -12562,7 +12520,7 @@
         <v>13</v>
       </c>
       <c r="F123" s="34" t="s">
-        <v>1084</v>
+        <v>1128</v>
       </c>
       <c r="G123" s="32" t="s">
         <v>13</v>
@@ -12612,10 +12570,10 @@
         <v>663</v>
       </c>
       <c r="B124" s="32" t="s">
-        <v>1107</v>
+        <v>1129</v>
       </c>
       <c r="C124" s="33" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
       <c r="D124" s="32" t="s">
         <v>653</v>
@@ -12624,7 +12582,7 @@
         <v>13</v>
       </c>
       <c r="F124" s="34" t="s">
-        <v>1109</v>
+        <v>736</v>
       </c>
       <c r="G124" s="32" t="s">
         <v>13</v>
@@ -12674,10 +12632,10 @@
         <v>663</v>
       </c>
       <c r="B125" s="32" t="s">
-        <v>1110</v>
+        <v>139</v>
       </c>
       <c r="C125" s="33" t="s">
-        <v>1108</v>
+        <v>1192</v>
       </c>
       <c r="D125" s="32" t="s">
         <v>653</v>
@@ -12686,7 +12644,7 @@
         <v>13</v>
       </c>
       <c r="F125" s="34" t="s">
-        <v>1109</v>
+        <v>1193</v>
       </c>
       <c r="G125" s="32" t="s">
         <v>13</v>
@@ -12736,10 +12694,10 @@
         <v>663</v>
       </c>
       <c r="B126" s="32" t="s">
-        <v>1114</v>
+        <v>801</v>
       </c>
       <c r="C126" s="33" t="s">
-        <v>1115</v>
+        <v>1194</v>
       </c>
       <c r="D126" s="32" t="s">
         <v>653</v>
@@ -12748,7 +12706,7 @@
         <v>13</v>
       </c>
       <c r="F126" s="34" t="s">
-        <v>1116</v>
+        <v>1195</v>
       </c>
       <c r="G126" s="32" t="s">
         <v>13</v>
@@ -12798,10 +12756,10 @@
         <v>663</v>
       </c>
       <c r="B127" s="32" t="s">
-        <v>1117</v>
+        <v>1201</v>
       </c>
       <c r="C127" s="33" t="s">
-        <v>1115</v>
+        <v>847</v>
       </c>
       <c r="D127" s="32" t="s">
         <v>653</v>
@@ -12810,7 +12768,7 @@
         <v>13</v>
       </c>
       <c r="F127" s="34" t="s">
-        <v>1116</v>
+        <v>1202</v>
       </c>
       <c r="G127" s="32" t="s">
         <v>13</v>
@@ -12860,10 +12818,10 @@
         <v>663</v>
       </c>
       <c r="B128" s="32" t="s">
-        <v>1140</v>
+        <v>1203</v>
       </c>
       <c r="C128" s="33" t="s">
-        <v>1141</v>
+        <v>847</v>
       </c>
       <c r="D128" s="32" t="s">
         <v>653</v>
@@ -12872,7 +12830,7 @@
         <v>13</v>
       </c>
       <c r="F128" s="34" t="s">
-        <v>1142</v>
+        <v>1204</v>
       </c>
       <c r="G128" s="32" t="s">
         <v>13</v>
@@ -12922,10 +12880,10 @@
         <v>663</v>
       </c>
       <c r="B129" s="32" t="s">
-        <v>1143</v>
+        <v>90</v>
       </c>
       <c r="C129" s="33" t="s">
-        <v>1141</v>
+        <v>1207</v>
       </c>
       <c r="D129" s="32" t="s">
         <v>653</v>
@@ -12934,7 +12892,7 @@
         <v>13</v>
       </c>
       <c r="F129" s="34" t="s">
-        <v>736</v>
+        <v>1208</v>
       </c>
       <c r="G129" s="32" t="s">
         <v>13</v>
@@ -12984,10 +12942,10 @@
         <v>663</v>
       </c>
       <c r="B130" s="32" t="s">
-        <v>139</v>
+        <v>932</v>
       </c>
       <c r="C130" s="33" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="D130" s="32" t="s">
         <v>653</v>
@@ -12996,7 +12954,7 @@
         <v>13</v>
       </c>
       <c r="F130" s="34" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="G130" s="32" t="s">
         <v>13</v>
@@ -13046,10 +13004,10 @@
         <v>663</v>
       </c>
       <c r="B131" s="32" t="s">
-        <v>801</v>
+        <v>874</v>
       </c>
       <c r="C131" s="33" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D131" s="32" t="s">
         <v>653</v>
@@ -13058,7 +13016,7 @@
         <v>13</v>
       </c>
       <c r="F131" s="34" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="G131" s="32" t="s">
         <v>13</v>
@@ -13108,10 +13066,10 @@
         <v>663</v>
       </c>
       <c r="B132" s="32" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="C132" s="33" t="s">
-        <v>847</v>
+        <v>1225</v>
       </c>
       <c r="D132" s="32" t="s">
         <v>653</v>
@@ -13120,7 +13078,7 @@
         <v>13</v>
       </c>
       <c r="F132" s="34" t="s">
-        <v>1216</v>
+        <v>752</v>
       </c>
       <c r="G132" s="32" t="s">
         <v>13</v>
@@ -13170,10 +13128,10 @@
         <v>663</v>
       </c>
       <c r="B133" s="32" t="s">
-        <v>1217</v>
+        <v>138</v>
       </c>
       <c r="C133" s="33" t="s">
-        <v>847</v>
+        <v>1225</v>
       </c>
       <c r="D133" s="32" t="s">
         <v>653</v>
@@ -13182,7 +13140,7 @@
         <v>13</v>
       </c>
       <c r="F133" s="34" t="s">
-        <v>1218</v>
+        <v>752</v>
       </c>
       <c r="G133" s="32" t="s">
         <v>13</v>
@@ -13232,10 +13190,10 @@
         <v>663</v>
       </c>
       <c r="B134" s="32" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="C134" s="33" t="s">
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="D134" s="32" t="s">
         <v>653</v>
@@ -13244,7 +13202,7 @@
         <v>13</v>
       </c>
       <c r="F134" s="34" t="s">
-        <v>1222</v>
+        <v>1227</v>
       </c>
       <c r="G134" s="32" t="s">
         <v>13</v>
@@ -13294,10 +13252,10 @@
         <v>663</v>
       </c>
       <c r="B135" s="32" t="s">
-        <v>932</v>
+        <v>23</v>
       </c>
       <c r="C135" s="33" t="s">
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="D135" s="32" t="s">
         <v>653</v>
@@ -13306,7 +13264,7 @@
         <v>13</v>
       </c>
       <c r="F135" s="34" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="G135" s="32" t="s">
         <v>13</v>
@@ -13356,10 +13314,10 @@
         <v>663</v>
       </c>
       <c r="B136" s="32" t="s">
-        <v>874</v>
+        <v>1252</v>
       </c>
       <c r="C136" s="33" t="s">
-        <v>1221</v>
+        <v>1253</v>
       </c>
       <c r="D136" s="32" t="s">
         <v>653</v>
@@ -13368,7 +13326,7 @@
         <v>13</v>
       </c>
       <c r="F136" s="34" t="s">
-        <v>1222</v>
+        <v>1095</v>
       </c>
       <c r="G136" s="32" t="s">
         <v>13</v>
@@ -13418,10 +13376,10 @@
         <v>663</v>
       </c>
       <c r="B137" s="32" t="s">
-        <v>1223</v>
+        <v>68</v>
       </c>
       <c r="C137" s="33" t="s">
-        <v>1239</v>
+        <v>761</v>
       </c>
       <c r="D137" s="32" t="s">
         <v>653</v>
@@ -13430,7 +13388,7 @@
         <v>13</v>
       </c>
       <c r="F137" s="34" t="s">
-        <v>752</v>
+        <v>1067</v>
       </c>
       <c r="G137" s="32" t="s">
         <v>13</v>
@@ -13480,10 +13438,10 @@
         <v>663</v>
       </c>
       <c r="B138" s="32" t="s">
-        <v>138</v>
+        <v>634</v>
       </c>
       <c r="C138" s="33" t="s">
-        <v>1239</v>
+        <v>1278</v>
       </c>
       <c r="D138" s="32" t="s">
         <v>653</v>
@@ -13492,7 +13450,7 @@
         <v>13</v>
       </c>
       <c r="F138" s="34" t="s">
-        <v>752</v>
+        <v>1193</v>
       </c>
       <c r="G138" s="32" t="s">
         <v>13</v>
@@ -13542,10 +13500,10 @@
         <v>663</v>
       </c>
       <c r="B139" s="32" t="s">
-        <v>68</v>
+        <v>1229</v>
       </c>
       <c r="C139" s="33" t="s">
-        <v>1240</v>
+        <v>1291</v>
       </c>
       <c r="D139" s="32" t="s">
         <v>653</v>
@@ -13554,7 +13512,7 @@
         <v>13</v>
       </c>
       <c r="F139" s="34" t="s">
-        <v>1241</v>
+        <v>1292</v>
       </c>
       <c r="G139" s="32" t="s">
         <v>13</v>
@@ -13604,10 +13562,10 @@
         <v>663</v>
       </c>
       <c r="B140" s="32" t="s">
-        <v>23</v>
+        <v>1209</v>
       </c>
       <c r="C140" s="33" t="s">
-        <v>1240</v>
+        <v>1328</v>
       </c>
       <c r="D140" s="32" t="s">
         <v>653</v>
@@ -13616,7 +13574,7 @@
         <v>13</v>
       </c>
       <c r="F140" s="34" t="s">
-        <v>1242</v>
+        <v>1329</v>
       </c>
       <c r="G140" s="32" t="s">
         <v>13</v>
@@ -13666,10 +13624,10 @@
         <v>663</v>
       </c>
       <c r="B141" s="32" t="s">
-        <v>1266</v>
+        <v>1330</v>
       </c>
       <c r="C141" s="33" t="s">
-        <v>1267</v>
+        <v>778</v>
       </c>
       <c r="D141" s="32" t="s">
         <v>653</v>
@@ -13678,7 +13636,7 @@
         <v>13</v>
       </c>
       <c r="F141" s="34" t="s">
-        <v>1109</v>
+        <v>779</v>
       </c>
       <c r="G141" s="32" t="s">
         <v>13</v>
@@ -13728,10 +13686,10 @@
         <v>663</v>
       </c>
       <c r="B142" s="32" t="s">
-        <v>68</v>
+        <v>801</v>
       </c>
       <c r="C142" s="33" t="s">
-        <v>761</v>
+        <v>1331</v>
       </c>
       <c r="D142" s="32" t="s">
         <v>653</v>
@@ -13740,7 +13698,7 @@
         <v>13</v>
       </c>
       <c r="F142" s="34" t="s">
-        <v>1081</v>
+        <v>1247</v>
       </c>
       <c r="G142" s="32" t="s">
         <v>13</v>
@@ -13790,10 +13748,10 @@
         <v>663</v>
       </c>
       <c r="B143" s="32" t="s">
-        <v>634</v>
+        <v>1341</v>
       </c>
       <c r="C143" s="33" t="s">
-        <v>1292</v>
+        <v>1342</v>
       </c>
       <c r="D143" s="32" t="s">
         <v>653</v>
@@ -13802,7 +13760,7 @@
         <v>13</v>
       </c>
       <c r="F143" s="34" t="s">
-        <v>1207</v>
+        <v>1343</v>
       </c>
       <c r="G143" s="32" t="s">
         <v>13</v>
@@ -13849,22 +13807,22 @@
     </row>
     <row r="144" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="32" t="s">
-        <v>663</v>
+        <v>20</v>
       </c>
       <c r="B144" s="32" t="s">
-        <v>1243</v>
+        <v>719</v>
       </c>
       <c r="C144" s="33" t="s">
-        <v>1305</v>
+        <v>697</v>
       </c>
       <c r="D144" s="32" t="s">
         <v>653</v>
       </c>
       <c r="E144" s="33" t="s">
-        <v>13</v>
+        <v>720</v>
       </c>
       <c r="F144" s="34" t="s">
-        <v>1306</v>
+        <v>721</v>
       </c>
       <c r="G144" s="32" t="s">
         <v>13</v>
@@ -13873,10 +13831,10 @@
         <v>13</v>
       </c>
       <c r="I144" s="32" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J144" s="33" t="s">
-        <v>13</v>
+        <v>722</v>
       </c>
       <c r="K144" s="32" t="s">
         <v>21</v>
@@ -13885,7 +13843,7 @@
         <v>13</v>
       </c>
       <c r="M144" s="32" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N144" s="32" t="s">
         <v>13</v>
@@ -13906,213 +13864,213 @@
         <v>13</v>
       </c>
       <c r="T144" s="32" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="32" t="s">
-        <v>663</v>
-      </c>
-      <c r="B145" s="32" t="s">
-        <v>1223</v>
-      </c>
-      <c r="C145" s="33" t="s">
-        <v>1342</v>
-      </c>
-      <c r="D145" s="32" t="s">
-        <v>653</v>
-      </c>
-      <c r="E145" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F145" s="34" t="s">
-        <v>1343</v>
-      </c>
-      <c r="G145" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H145" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="I145" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="J145" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="K145" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="L145" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="M145" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="N145" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="O145" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="P145" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q145" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="R145" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="S145" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="T145" s="32" t="s">
-        <v>13</v>
+      <c r="A145" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B145" s="29" t="s">
+        <v>705</v>
+      </c>
+      <c r="C145" s="30" t="s">
+        <v>706</v>
+      </c>
+      <c r="D145" s="29" t="s">
+        <v>700</v>
+      </c>
+      <c r="E145" s="30" t="s">
+        <v>707</v>
+      </c>
+      <c r="F145" s="31" t="s">
+        <v>708</v>
+      </c>
+      <c r="G145" s="29" t="s">
+        <v>703</v>
+      </c>
+      <c r="H145" s="29" t="s">
+        <v>634</v>
+      </c>
+      <c r="I145" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="J145" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="K145" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="L145" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="M145" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="N145" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="O145" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P145" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q145" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="R145" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="S145" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="T145" s="29" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="146" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="32" t="s">
-        <v>663</v>
-      </c>
-      <c r="B146" s="32" t="s">
-        <v>1344</v>
-      </c>
-      <c r="C146" s="33" t="s">
-        <v>778</v>
-      </c>
-      <c r="D146" s="32" t="s">
-        <v>653</v>
-      </c>
-      <c r="E146" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F146" s="34" t="s">
-        <v>779</v>
-      </c>
-      <c r="G146" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H146" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="I146" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="J146" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="K146" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="L146" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="M146" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="N146" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="O146" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="P146" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q146" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="R146" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="S146" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="T146" s="32" t="s">
-        <v>13</v>
+      <c r="A146" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B146" s="29" t="s">
+        <v>709</v>
+      </c>
+      <c r="C146" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="D146" s="29" t="s">
+        <v>700</v>
+      </c>
+      <c r="E146" s="30" t="s">
+        <v>710</v>
+      </c>
+      <c r="F146" s="31" t="s">
+        <v>711</v>
+      </c>
+      <c r="G146" s="29" t="s">
+        <v>703</v>
+      </c>
+      <c r="H146" s="29" t="s">
+        <v>634</v>
+      </c>
+      <c r="I146" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="J146" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="K146" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="L146" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="M146" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="N146" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="O146" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P146" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q146" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="R146" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="S146" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="T146" s="29" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="147" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="32" t="s">
-        <v>663</v>
-      </c>
-      <c r="B147" s="32" t="s">
-        <v>801</v>
-      </c>
-      <c r="C147" s="33" t="s">
-        <v>1345</v>
-      </c>
-      <c r="D147" s="32" t="s">
-        <v>653</v>
-      </c>
-      <c r="E147" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F147" s="34" t="s">
-        <v>1261</v>
-      </c>
-      <c r="G147" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H147" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="I147" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="J147" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="K147" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="L147" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="M147" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="N147" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="O147" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="P147" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q147" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="R147" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="S147" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="T147" s="32" t="s">
-        <v>13</v>
+      <c r="A147" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B147" s="29" t="s">
+        <v>699</v>
+      </c>
+      <c r="C147" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="D147" s="29" t="s">
+        <v>700</v>
+      </c>
+      <c r="E147" s="30" t="s">
+        <v>701</v>
+      </c>
+      <c r="F147" s="31" t="s">
+        <v>702</v>
+      </c>
+      <c r="G147" s="29" t="s">
+        <v>703</v>
+      </c>
+      <c r="H147" s="29" t="s">
+        <v>634</v>
+      </c>
+      <c r="I147" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="J147" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="K147" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="L147" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="M147" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="N147" s="29" t="s">
+        <v>1050</v>
+      </c>
+      <c r="O147" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P147" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q147" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="R147" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="S147" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="T147" s="29" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="148" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="32" t="s">
-        <v>663</v>
+        <v>715</v>
       </c>
       <c r="B148" s="32" t="s">
-        <v>1355</v>
+        <v>716</v>
       </c>
       <c r="C148" s="33" t="s">
-        <v>1356</v>
+        <v>1062</v>
       </c>
       <c r="D148" s="32" t="s">
-        <v>653</v>
+        <v>700</v>
       </c>
       <c r="E148" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F148" s="34" t="s">
-        <v>1357</v>
+        <v>717</v>
       </c>
       <c r="G148" s="32" t="s">
         <v>13</v>
@@ -14121,10 +14079,10 @@
         <v>13</v>
       </c>
       <c r="I148" s="32" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="J148" s="33" t="s">
-        <v>13</v>
+        <v>718</v>
       </c>
       <c r="K148" s="32" t="s">
         <v>21</v>
@@ -14133,7 +14091,7 @@
         <v>13</v>
       </c>
       <c r="M148" s="32" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="N148" s="32" t="s">
         <v>13</v>
@@ -14154,27 +14112,27 @@
         <v>13</v>
       </c>
       <c r="T148" s="32" t="s">
-        <v>13</v>
+        <v>278</v>
       </c>
     </row>
     <row r="149" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="32" t="s">
-        <v>20</v>
+        <v>663</v>
       </c>
       <c r="B149" s="32" t="s">
-        <v>719</v>
+        <v>1063</v>
       </c>
       <c r="C149" s="33" t="s">
-        <v>697</v>
+        <v>1064</v>
       </c>
       <c r="D149" s="32" t="s">
-        <v>653</v>
+        <v>700</v>
       </c>
       <c r="E149" s="33" t="s">
-        <v>720</v>
+        <v>13</v>
       </c>
       <c r="F149" s="34" t="s">
-        <v>721</v>
+        <v>1065</v>
       </c>
       <c r="G149" s="32" t="s">
         <v>13</v>
@@ -14183,10 +14141,10 @@
         <v>13</v>
       </c>
       <c r="I149" s="32" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J149" s="33" t="s">
-        <v>722</v>
+        <v>13</v>
       </c>
       <c r="K149" s="32" t="s">
         <v>21</v>
@@ -14195,7 +14153,7 @@
         <v>13</v>
       </c>
       <c r="M149" s="32" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N149" s="32" t="s">
         <v>13</v>
@@ -14216,204 +14174,204 @@
         <v>13</v>
       </c>
       <c r="T149" s="32" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="150" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B150" s="29" t="s">
-        <v>705</v>
-      </c>
-      <c r="C150" s="30" t="s">
-        <v>706</v>
-      </c>
-      <c r="D150" s="29" t="s">
+      <c r="A150" s="32" t="s">
+        <v>663</v>
+      </c>
+      <c r="B150" s="32" t="s">
+        <v>634</v>
+      </c>
+      <c r="C150" s="33" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D150" s="32" t="s">
         <v>700</v>
       </c>
-      <c r="E150" s="30" t="s">
-        <v>707</v>
-      </c>
-      <c r="F150" s="31" t="s">
-        <v>708</v>
-      </c>
-      <c r="G150" s="29" t="s">
-        <v>703</v>
-      </c>
-      <c r="H150" s="29" t="s">
-        <v>634</v>
-      </c>
-      <c r="I150" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="J150" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="K150" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="L150" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="M150" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="N150" s="29" t="s">
-        <v>1062</v>
-      </c>
-      <c r="O150" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="P150" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q150" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="R150" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="S150" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="T150" s="29" t="s">
-        <v>30</v>
+      <c r="E150" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F150" s="34" t="s">
+        <v>443</v>
+      </c>
+      <c r="G150" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H150" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="I150" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="J150" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="K150" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L150" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="M150" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="N150" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="O150" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="P150" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q150" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="R150" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="S150" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="T150" s="32" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="151" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B151" s="29" t="s">
-        <v>709</v>
-      </c>
-      <c r="C151" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="D151" s="29" t="s">
+      <c r="A151" s="32" t="s">
+        <v>663</v>
+      </c>
+      <c r="B151" s="32" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C151" s="33" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D151" s="32" t="s">
         <v>700</v>
       </c>
-      <c r="E151" s="30" t="s">
-        <v>710</v>
-      </c>
-      <c r="F151" s="31" t="s">
-        <v>711</v>
-      </c>
-      <c r="G151" s="29" t="s">
-        <v>703</v>
-      </c>
-      <c r="H151" s="29" t="s">
-        <v>634</v>
-      </c>
-      <c r="I151" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="J151" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="K151" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="L151" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="M151" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="N151" s="29" t="s">
-        <v>1063</v>
-      </c>
-      <c r="O151" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="P151" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q151" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="R151" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="S151" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="T151" s="29" t="s">
-        <v>30</v>
+      <c r="E151" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F151" s="34" t="s">
+        <v>1086</v>
+      </c>
+      <c r="G151" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H151" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="I151" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="J151" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="K151" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L151" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="M151" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="N151" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="O151" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="P151" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q151" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="R151" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="S151" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="T151" s="32" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="152" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B152" s="29" t="s">
-        <v>699</v>
-      </c>
-      <c r="C152" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="D152" s="29" t="s">
+      <c r="A152" s="32" t="s">
+        <v>663</v>
+      </c>
+      <c r="B152" s="32" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C152" s="33" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D152" s="32" t="s">
         <v>700</v>
       </c>
-      <c r="E152" s="30" t="s">
-        <v>701</v>
-      </c>
-      <c r="F152" s="31" t="s">
-        <v>702</v>
-      </c>
-      <c r="G152" s="29" t="s">
-        <v>703</v>
-      </c>
-      <c r="H152" s="29" t="s">
-        <v>634</v>
-      </c>
-      <c r="I152" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="J152" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="K152" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="L152" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="M152" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="N152" s="29" t="s">
-        <v>1064</v>
-      </c>
-      <c r="O152" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="P152" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q152" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="R152" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="S152" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="T152" s="29" t="s">
-        <v>30</v>
+      <c r="E152" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F152" s="34" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G152" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H152" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="I152" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="J152" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="K152" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L152" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="M152" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="N152" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="O152" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="P152" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q152" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="R152" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="S152" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="T152" s="32" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="153" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="32" t="s">
-        <v>715</v>
+        <v>663</v>
       </c>
       <c r="B153" s="32" t="s">
-        <v>716</v>
+        <v>1090</v>
       </c>
       <c r="C153" s="33" t="s">
-        <v>1076</v>
+        <v>1091</v>
       </c>
       <c r="D153" s="32" t="s">
         <v>700</v>
@@ -14422,7 +14380,7 @@
         <v>13</v>
       </c>
       <c r="F153" s="34" t="s">
-        <v>717</v>
+        <v>1092</v>
       </c>
       <c r="G153" s="32" t="s">
         <v>13</v>
@@ -14431,10 +14389,10 @@
         <v>13</v>
       </c>
       <c r="I153" s="32" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J153" s="33" t="s">
-        <v>718</v>
+        <v>13</v>
       </c>
       <c r="K153" s="32" t="s">
         <v>21</v>
@@ -14443,7 +14401,7 @@
         <v>13</v>
       </c>
       <c r="M153" s="32" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="N153" s="32" t="s">
         <v>13</v>
@@ -14464,7 +14422,7 @@
         <v>13</v>
       </c>
       <c r="T153" s="32" t="s">
-        <v>278</v>
+        <v>13</v>
       </c>
     </row>
     <row r="154" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14472,10 +14430,10 @@
         <v>663</v>
       </c>
       <c r="B154" s="32" t="s">
-        <v>1077</v>
+        <v>634</v>
       </c>
       <c r="C154" s="33" t="s">
-        <v>1078</v>
+        <v>1106</v>
       </c>
       <c r="D154" s="32" t="s">
         <v>700</v>
@@ -14484,7 +14442,7 @@
         <v>13</v>
       </c>
       <c r="F154" s="34" t="s">
-        <v>1079</v>
+        <v>1107</v>
       </c>
       <c r="G154" s="32" t="s">
         <v>13</v>
@@ -14534,10 +14492,10 @@
         <v>663</v>
       </c>
       <c r="B155" s="32" t="s">
-        <v>634</v>
+        <v>669</v>
       </c>
       <c r="C155" s="33" t="s">
-        <v>1089</v>
+        <v>1106</v>
       </c>
       <c r="D155" s="32" t="s">
         <v>700</v>
@@ -14546,7 +14504,7 @@
         <v>13</v>
       </c>
       <c r="F155" s="34" t="s">
-        <v>443</v>
+        <v>1108</v>
       </c>
       <c r="G155" s="32" t="s">
         <v>13</v>
@@ -14596,10 +14554,10 @@
         <v>663</v>
       </c>
       <c r="B156" s="32" t="s">
-        <v>1098</v>
+        <v>171</v>
       </c>
       <c r="C156" s="33" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="D156" s="32" t="s">
         <v>700</v>
@@ -14608,7 +14566,7 @@
         <v>13</v>
       </c>
       <c r="F156" s="34" t="s">
-        <v>1100</v>
+        <v>1109</v>
       </c>
       <c r="G156" s="32" t="s">
         <v>13</v>
@@ -14658,10 +14616,10 @@
         <v>663</v>
       </c>
       <c r="B157" s="32" t="s">
-        <v>1101</v>
+        <v>650</v>
       </c>
       <c r="C157" s="33" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="D157" s="32" t="s">
         <v>700</v>
@@ -14670,7 +14628,7 @@
         <v>13</v>
       </c>
       <c r="F157" s="34" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="G157" s="32" t="s">
         <v>13</v>
@@ -14720,10 +14678,10 @@
         <v>663</v>
       </c>
       <c r="B158" s="32" t="s">
-        <v>1104</v>
+        <v>1112</v>
       </c>
       <c r="C158" s="33" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
       <c r="D158" s="32" t="s">
         <v>700</v>
@@ -14732,7 +14690,7 @@
         <v>13</v>
       </c>
       <c r="F158" s="34" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="G158" s="32" t="s">
         <v>13</v>
@@ -14782,10 +14740,10 @@
         <v>663</v>
       </c>
       <c r="B159" s="32" t="s">
-        <v>634</v>
+        <v>1130</v>
       </c>
       <c r="C159" s="33" t="s">
-        <v>1120</v>
+        <v>1131</v>
       </c>
       <c r="D159" s="32" t="s">
         <v>700</v>
@@ -14794,7 +14752,7 @@
         <v>13</v>
       </c>
       <c r="F159" s="34" t="s">
-        <v>1121</v>
+        <v>1132</v>
       </c>
       <c r="G159" s="32" t="s">
         <v>13</v>
@@ -14844,10 +14802,10 @@
         <v>663</v>
       </c>
       <c r="B160" s="32" t="s">
-        <v>669</v>
+        <v>1080</v>
       </c>
       <c r="C160" s="33" t="s">
-        <v>1120</v>
+        <v>1154</v>
       </c>
       <c r="D160" s="32" t="s">
         <v>700</v>
@@ -14856,7 +14814,7 @@
         <v>13</v>
       </c>
       <c r="F160" s="34" t="s">
-        <v>1122</v>
+        <v>1155</v>
       </c>
       <c r="G160" s="32" t="s">
         <v>13</v>
@@ -14906,10 +14864,10 @@
         <v>663</v>
       </c>
       <c r="B161" s="32" t="s">
-        <v>171</v>
+        <v>1165</v>
       </c>
       <c r="C161" s="33" t="s">
-        <v>1120</v>
+        <v>1166</v>
       </c>
       <c r="D161" s="32" t="s">
         <v>700</v>
@@ -14918,7 +14876,7 @@
         <v>13</v>
       </c>
       <c r="F161" s="34" t="s">
-        <v>1123</v>
+        <v>1167</v>
       </c>
       <c r="G161" s="32" t="s">
         <v>13</v>
@@ -14968,10 +14926,10 @@
         <v>663</v>
       </c>
       <c r="B162" s="32" t="s">
-        <v>650</v>
+        <v>1168</v>
       </c>
       <c r="C162" s="33" t="s">
-        <v>1120</v>
+        <v>1166</v>
       </c>
       <c r="D162" s="32" t="s">
         <v>700</v>
@@ -14980,7 +14938,7 @@
         <v>13</v>
       </c>
       <c r="F162" s="34" t="s">
-        <v>1124</v>
+        <v>1167</v>
       </c>
       <c r="G162" s="32" t="s">
         <v>13</v>
@@ -15030,10 +14988,10 @@
         <v>663</v>
       </c>
       <c r="B163" s="32" t="s">
-        <v>1126</v>
+        <v>1169</v>
       </c>
       <c r="C163" s="33" t="s">
-        <v>1127</v>
+        <v>1166</v>
       </c>
       <c r="D163" s="32" t="s">
         <v>700</v>
@@ -15042,7 +15000,7 @@
         <v>13</v>
       </c>
       <c r="F163" s="34" t="s">
-        <v>1128</v>
+        <v>1170</v>
       </c>
       <c r="G163" s="32" t="s">
         <v>13</v>
@@ -15092,10 +15050,10 @@
         <v>663</v>
       </c>
       <c r="B164" s="32" t="s">
-        <v>1144</v>
+        <v>1171</v>
       </c>
       <c r="C164" s="33" t="s">
-        <v>1145</v>
+        <v>1172</v>
       </c>
       <c r="D164" s="32" t="s">
         <v>700</v>
@@ -15104,7 +15062,7 @@
         <v>13</v>
       </c>
       <c r="F164" s="34" t="s">
-        <v>1146</v>
+        <v>1022</v>
       </c>
       <c r="G164" s="32" t="s">
         <v>13</v>
@@ -15154,10 +15112,10 @@
         <v>663</v>
       </c>
       <c r="B165" s="32" t="s">
-        <v>1094</v>
+        <v>1173</v>
       </c>
       <c r="C165" s="33" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="D165" s="32" t="s">
         <v>700</v>
@@ -15166,7 +15124,7 @@
         <v>13</v>
       </c>
       <c r="F165" s="34" t="s">
-        <v>1169</v>
+        <v>1174</v>
       </c>
       <c r="G165" s="32" t="s">
         <v>13</v>
@@ -15216,10 +15174,10 @@
         <v>663</v>
       </c>
       <c r="B166" s="32" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C166" s="33" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="D166" s="32" t="s">
         <v>700</v>
@@ -15228,7 +15186,7 @@
         <v>13</v>
       </c>
       <c r="F166" s="34" t="s">
-        <v>1181</v>
+        <v>1143</v>
       </c>
       <c r="G166" s="32" t="s">
         <v>13</v>
@@ -15278,10 +15236,10 @@
         <v>663</v>
       </c>
       <c r="B167" s="32" t="s">
-        <v>1182</v>
+        <v>631</v>
       </c>
       <c r="C167" s="33" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="D167" s="32" t="s">
         <v>700</v>
@@ -15290,7 +15248,7 @@
         <v>13</v>
       </c>
       <c r="F167" s="34" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G167" s="32" t="s">
         <v>13</v>
@@ -15340,10 +15298,10 @@
         <v>663</v>
       </c>
       <c r="B168" s="32" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C168" s="33" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="D168" s="32" t="s">
         <v>700</v>
@@ -15352,7 +15310,7 @@
         <v>13</v>
       </c>
       <c r="F168" s="34" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G168" s="32" t="s">
         <v>13</v>
@@ -15402,10 +15360,10 @@
         <v>663</v>
       </c>
       <c r="B169" s="32" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C169" s="33" t="s">
-        <v>1186</v>
+        <v>1200</v>
       </c>
       <c r="D169" s="32" t="s">
         <v>700</v>
@@ -15414,7 +15372,7 @@
         <v>13</v>
       </c>
       <c r="F169" s="34" t="s">
-        <v>1022</v>
+        <v>1095</v>
       </c>
       <c r="G169" s="32" t="s">
         <v>13</v>
@@ -15464,10 +15422,10 @@
         <v>663</v>
       </c>
       <c r="B170" s="32" t="s">
-        <v>1187</v>
+        <v>1209</v>
       </c>
       <c r="C170" s="33" t="s">
-        <v>1186</v>
+        <v>1210</v>
       </c>
       <c r="D170" s="32" t="s">
         <v>700</v>
@@ -15476,7 +15434,7 @@
         <v>13</v>
       </c>
       <c r="F170" s="34" t="s">
-        <v>1188</v>
+        <v>1211</v>
       </c>
       <c r="G170" s="32" t="s">
         <v>13</v>
@@ -15526,10 +15484,10 @@
         <v>663</v>
       </c>
       <c r="B171" s="32" t="s">
-        <v>1191</v>
+        <v>631</v>
       </c>
       <c r="C171" s="33" t="s">
-        <v>1192</v>
+        <v>1223</v>
       </c>
       <c r="D171" s="32" t="s">
         <v>700</v>
@@ -15538,7 +15496,7 @@
         <v>13</v>
       </c>
       <c r="F171" s="34" t="s">
-        <v>1157</v>
+        <v>1224</v>
       </c>
       <c r="G171" s="32" t="s">
         <v>13</v>
@@ -15588,10 +15546,10 @@
         <v>663</v>
       </c>
       <c r="B172" s="32" t="s">
-        <v>631</v>
+        <v>1231</v>
       </c>
       <c r="C172" s="33" t="s">
-        <v>1193</v>
+        <v>1232</v>
       </c>
       <c r="D172" s="32" t="s">
         <v>700</v>
@@ -15600,7 +15558,7 @@
         <v>13</v>
       </c>
       <c r="F172" s="34" t="s">
-        <v>1194</v>
+        <v>1233</v>
       </c>
       <c r="G172" s="32" t="s">
         <v>13</v>
@@ -15650,10 +15608,10 @@
         <v>663</v>
       </c>
       <c r="B173" s="32" t="s">
-        <v>1195</v>
+        <v>133</v>
       </c>
       <c r="C173" s="33" t="s">
-        <v>1196</v>
+        <v>1241</v>
       </c>
       <c r="D173" s="32" t="s">
         <v>700</v>
@@ -15662,7 +15620,7 @@
         <v>13</v>
       </c>
       <c r="F173" s="34" t="s">
-        <v>1197</v>
+        <v>1242</v>
       </c>
       <c r="G173" s="32" t="s">
         <v>13</v>
@@ -15712,19 +15670,19 @@
         <v>663</v>
       </c>
       <c r="B174" s="32" t="s">
-        <v>1200</v>
+        <v>1072</v>
       </c>
       <c r="C174" s="33" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="D174" s="32" t="s">
-        <v>700</v>
+        <v>638</v>
       </c>
       <c r="E174" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F174" s="34" t="s">
-        <v>1109</v>
+        <v>1213</v>
       </c>
       <c r="G174" s="32" t="s">
         <v>13</v>
@@ -15754,7 +15712,7 @@
         <v>13</v>
       </c>
       <c r="P174" s="33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q174" s="33" t="s">
         <v>13</v>
@@ -15774,19 +15732,19 @@
         <v>663</v>
       </c>
       <c r="B175" s="32" t="s">
-        <v>1223</v>
+        <v>1214</v>
       </c>
       <c r="C175" s="33" t="s">
-        <v>1224</v>
+        <v>1212</v>
       </c>
       <c r="D175" s="32" t="s">
-        <v>700</v>
+        <v>638</v>
       </c>
       <c r="E175" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F175" s="34" t="s">
-        <v>1225</v>
+        <v>1215</v>
       </c>
       <c r="G175" s="32" t="s">
         <v>13</v>
@@ -15816,7 +15774,7 @@
         <v>13</v>
       </c>
       <c r="P175" s="33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q175" s="33" t="s">
         <v>13</v>
@@ -15836,10 +15794,10 @@
         <v>663</v>
       </c>
       <c r="B176" s="32" t="s">
-        <v>631</v>
+        <v>1209</v>
       </c>
       <c r="C176" s="33" t="s">
-        <v>1237</v>
+        <v>1246</v>
       </c>
       <c r="D176" s="32" t="s">
         <v>700</v>
@@ -15848,7 +15806,7 @@
         <v>13</v>
       </c>
       <c r="F176" s="34" t="s">
-        <v>1238</v>
+        <v>1247</v>
       </c>
       <c r="G176" s="32" t="s">
         <v>13</v>
@@ -15898,10 +15856,10 @@
         <v>663</v>
       </c>
       <c r="B177" s="32" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
       <c r="C177" s="33" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
       <c r="D177" s="32" t="s">
         <v>700</v>
@@ -15910,7 +15868,7 @@
         <v>13</v>
       </c>
       <c r="F177" s="34" t="s">
-        <v>1247</v>
+        <v>754</v>
       </c>
       <c r="G177" s="32" t="s">
         <v>13</v>
@@ -15960,7 +15918,7 @@
         <v>663</v>
       </c>
       <c r="B178" s="32" t="s">
-        <v>133</v>
+        <v>1254</v>
       </c>
       <c r="C178" s="33" t="s">
         <v>1255</v>
@@ -16022,19 +15980,19 @@
         <v>663</v>
       </c>
       <c r="B179" s="32" t="s">
-        <v>1086</v>
+        <v>1117</v>
       </c>
       <c r="C179" s="33" t="s">
-        <v>1226</v>
+        <v>1257</v>
       </c>
       <c r="D179" s="32" t="s">
-        <v>638</v>
+        <v>700</v>
       </c>
       <c r="E179" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F179" s="34" t="s">
-        <v>1227</v>
+        <v>1258</v>
       </c>
       <c r="G179" s="32" t="s">
         <v>13</v>
@@ -16064,7 +16022,7 @@
         <v>13</v>
       </c>
       <c r="P179" s="33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q179" s="33" t="s">
         <v>13</v>
@@ -16084,19 +16042,19 @@
         <v>663</v>
       </c>
       <c r="B180" s="32" t="s">
-        <v>1228</v>
+        <v>23</v>
       </c>
       <c r="C180" s="33" t="s">
-        <v>1226</v>
+        <v>1283</v>
       </c>
       <c r="D180" s="32" t="s">
-        <v>638</v>
+        <v>700</v>
       </c>
       <c r="E180" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F180" s="34" t="s">
-        <v>1229</v>
+        <v>1284</v>
       </c>
       <c r="G180" s="32" t="s">
         <v>13</v>
@@ -16126,7 +16084,7 @@
         <v>13</v>
       </c>
       <c r="P180" s="33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q180" s="33" t="s">
         <v>13</v>
@@ -16146,10 +16104,10 @@
         <v>663</v>
       </c>
       <c r="B181" s="32" t="s">
-        <v>1223</v>
+        <v>634</v>
       </c>
       <c r="C181" s="33" t="s">
-        <v>1260</v>
+        <v>1283</v>
       </c>
       <c r="D181" s="32" t="s">
         <v>700</v>
@@ -16158,7 +16116,7 @@
         <v>13</v>
       </c>
       <c r="F181" s="34" t="s">
-        <v>1261</v>
+        <v>1285</v>
       </c>
       <c r="G181" s="32" t="s">
         <v>13</v>
@@ -16208,10 +16166,10 @@
         <v>663</v>
       </c>
       <c r="B182" s="32" t="s">
-        <v>1264</v>
+        <v>669</v>
       </c>
       <c r="C182" s="33" t="s">
-        <v>1265</v>
+        <v>1283</v>
       </c>
       <c r="D182" s="32" t="s">
         <v>700</v>
@@ -16220,7 +16178,7 @@
         <v>13</v>
       </c>
       <c r="F182" s="34" t="s">
-        <v>754</v>
+        <v>1285</v>
       </c>
       <c r="G182" s="32" t="s">
         <v>13</v>
@@ -16270,10 +16228,10 @@
         <v>663</v>
       </c>
       <c r="B183" s="32" t="s">
-        <v>1268</v>
+        <v>1288</v>
       </c>
       <c r="C183" s="33" t="s">
-        <v>1269</v>
+        <v>1289</v>
       </c>
       <c r="D183" s="32" t="s">
         <v>700</v>
@@ -16282,7 +16240,7 @@
         <v>13</v>
       </c>
       <c r="F183" s="34" t="s">
-        <v>1270</v>
+        <v>1290</v>
       </c>
       <c r="G183" s="32" t="s">
         <v>13</v>
@@ -16332,10 +16290,10 @@
         <v>663</v>
       </c>
       <c r="B184" s="32" t="s">
-        <v>1131</v>
+        <v>1293</v>
       </c>
       <c r="C184" s="33" t="s">
-        <v>1271</v>
+        <v>1294</v>
       </c>
       <c r="D184" s="32" t="s">
         <v>700</v>
@@ -16344,7 +16302,7 @@
         <v>13</v>
       </c>
       <c r="F184" s="34" t="s">
-        <v>1272</v>
+        <v>1295</v>
       </c>
       <c r="G184" s="32" t="s">
         <v>13</v>
@@ -16394,10 +16352,10 @@
         <v>663</v>
       </c>
       <c r="B185" s="32" t="s">
-        <v>23</v>
+        <v>1303</v>
       </c>
       <c r="C185" s="33" t="s">
-        <v>1297</v>
+        <v>768</v>
       </c>
       <c r="D185" s="32" t="s">
         <v>700</v>
@@ -16406,7 +16364,7 @@
         <v>13</v>
       </c>
       <c r="F185" s="34" t="s">
-        <v>1298</v>
+        <v>1219</v>
       </c>
       <c r="G185" s="32" t="s">
         <v>13</v>
@@ -16456,10 +16414,10 @@
         <v>663</v>
       </c>
       <c r="B186" s="32" t="s">
-        <v>634</v>
+        <v>758</v>
       </c>
       <c r="C186" s="33" t="s">
-        <v>1297</v>
+        <v>1304</v>
       </c>
       <c r="D186" s="32" t="s">
         <v>700</v>
@@ -16468,7 +16426,7 @@
         <v>13</v>
       </c>
       <c r="F186" s="34" t="s">
-        <v>1299</v>
+        <v>1067</v>
       </c>
       <c r="G186" s="32" t="s">
         <v>13</v>
@@ -16518,10 +16476,10 @@
         <v>663</v>
       </c>
       <c r="B187" s="32" t="s">
-        <v>669</v>
+        <v>1305</v>
       </c>
       <c r="C187" s="33" t="s">
-        <v>1297</v>
+        <v>1304</v>
       </c>
       <c r="D187" s="32" t="s">
         <v>700</v>
@@ -16530,7 +16488,7 @@
         <v>13</v>
       </c>
       <c r="F187" s="34" t="s">
-        <v>1299</v>
+        <v>1067</v>
       </c>
       <c r="G187" s="32" t="s">
         <v>13</v>
@@ -16580,10 +16538,10 @@
         <v>663</v>
       </c>
       <c r="B188" s="32" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C188" s="33" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="D188" s="32" t="s">
         <v>700</v>
@@ -16592,7 +16550,7 @@
         <v>13</v>
       </c>
       <c r="F188" s="34" t="s">
-        <v>1304</v>
+        <v>1067</v>
       </c>
       <c r="G188" s="32" t="s">
         <v>13</v>
@@ -16642,19 +16600,19 @@
         <v>663</v>
       </c>
       <c r="B189" s="32" t="s">
-        <v>1307</v>
+        <v>1229</v>
       </c>
       <c r="C189" s="33" t="s">
-        <v>1308</v>
+        <v>848</v>
       </c>
       <c r="D189" s="32" t="s">
-        <v>700</v>
+        <v>653</v>
       </c>
       <c r="E189" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F189" s="34" t="s">
-        <v>1309</v>
+        <v>1230</v>
       </c>
       <c r="G189" s="32" t="s">
         <v>13</v>
@@ -16684,7 +16642,7 @@
         <v>13</v>
       </c>
       <c r="P189" s="33" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="Q189" s="33" t="s">
         <v>13</v>
@@ -16704,10 +16662,10 @@
         <v>663</v>
       </c>
       <c r="B190" s="32" t="s">
-        <v>1317</v>
+        <v>1237</v>
       </c>
       <c r="C190" s="33" t="s">
-        <v>768</v>
+        <v>1312</v>
       </c>
       <c r="D190" s="32" t="s">
         <v>700</v>
@@ -16716,7 +16674,7 @@
         <v>13</v>
       </c>
       <c r="F190" s="34" t="s">
-        <v>1233</v>
+        <v>1313</v>
       </c>
       <c r="G190" s="32" t="s">
         <v>13</v>
@@ -16766,10 +16724,10 @@
         <v>663</v>
       </c>
       <c r="B191" s="32" t="s">
-        <v>758</v>
+        <v>1238</v>
       </c>
       <c r="C191" s="33" t="s">
-        <v>1318</v>
+        <v>1312</v>
       </c>
       <c r="D191" s="32" t="s">
         <v>700</v>
@@ -16778,7 +16736,7 @@
         <v>13</v>
       </c>
       <c r="F191" s="34" t="s">
-        <v>1081</v>
+        <v>1019</v>
       </c>
       <c r="G191" s="32" t="s">
         <v>13</v>
@@ -16828,10 +16786,10 @@
         <v>663</v>
       </c>
       <c r="B192" s="32" t="s">
-        <v>1319</v>
+        <v>1314</v>
       </c>
       <c r="C192" s="33" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="D192" s="32" t="s">
         <v>700</v>
@@ -16840,7 +16798,7 @@
         <v>13</v>
       </c>
       <c r="F192" s="34" t="s">
-        <v>1081</v>
+        <v>1001</v>
       </c>
       <c r="G192" s="32" t="s">
         <v>13</v>
@@ -16890,10 +16848,10 @@
         <v>663</v>
       </c>
       <c r="B193" s="32" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="C193" s="33" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="D193" s="32" t="s">
         <v>700</v>
@@ -16902,7 +16860,7 @@
         <v>13</v>
       </c>
       <c r="F193" s="34" t="s">
-        <v>1081</v>
+        <v>1318</v>
       </c>
       <c r="G193" s="32" t="s">
         <v>13</v>
@@ -16952,19 +16910,19 @@
         <v>663</v>
       </c>
       <c r="B194" s="32" t="s">
-        <v>1243</v>
+        <v>1325</v>
       </c>
       <c r="C194" s="33" t="s">
-        <v>848</v>
+        <v>1326</v>
       </c>
       <c r="D194" s="32" t="s">
-        <v>653</v>
+        <v>700</v>
       </c>
       <c r="E194" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F194" s="34" t="s">
-        <v>1244</v>
+        <v>1327</v>
       </c>
       <c r="G194" s="32" t="s">
         <v>13</v>
@@ -16994,7 +16952,7 @@
         <v>13</v>
       </c>
       <c r="P194" s="33" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="Q194" s="33" t="s">
         <v>13</v>
@@ -17010,65 +16968,65 @@
       </c>
     </row>
     <row r="195" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="32" t="s">
-        <v>663</v>
-      </c>
-      <c r="B195" s="32" t="s">
-        <v>1251</v>
-      </c>
-      <c r="C195" s="33" t="s">
-        <v>1326</v>
-      </c>
-      <c r="D195" s="32" t="s">
-        <v>700</v>
-      </c>
-      <c r="E195" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F195" s="34" t="s">
-        <v>1327</v>
-      </c>
-      <c r="G195" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H195" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="I195" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="J195" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="K195" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="L195" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="M195" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="N195" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="O195" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="P195" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q195" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="R195" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="S195" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="T195" s="32" t="s">
-        <v>13</v>
+      <c r="A195" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B195" s="29" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C195" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="D195" s="29" t="s">
+        <v>712</v>
+      </c>
+      <c r="E195" s="30" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F195" s="31" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G195" s="29" t="s">
+        <v>713</v>
+      </c>
+      <c r="H195" s="29" t="s">
+        <v>669</v>
+      </c>
+      <c r="I195" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="J195" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="K195" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="L195" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="M195" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="N195" s="29" t="s">
+        <v>1060</v>
+      </c>
+      <c r="O195" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="P195" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q195" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="R195" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="S195" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="T195" s="29" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="196" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17076,19 +17034,19 @@
         <v>663</v>
       </c>
       <c r="B196" s="32" t="s">
-        <v>1252</v>
+        <v>1072</v>
       </c>
       <c r="C196" s="33" t="s">
-        <v>1326</v>
+        <v>1073</v>
       </c>
       <c r="D196" s="32" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="E196" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F196" s="34" t="s">
-        <v>1019</v>
+        <v>1074</v>
       </c>
       <c r="G196" s="32" t="s">
         <v>13</v>
@@ -17138,19 +17096,19 @@
         <v>663</v>
       </c>
       <c r="B197" s="32" t="s">
-        <v>1328</v>
+        <v>133</v>
       </c>
       <c r="C197" s="33" t="s">
-        <v>1329</v>
+        <v>1076</v>
       </c>
       <c r="D197" s="32" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="E197" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F197" s="34" t="s">
-        <v>1001</v>
+        <v>244</v>
       </c>
       <c r="G197" s="32" t="s">
         <v>13</v>
@@ -17200,19 +17158,19 @@
         <v>663</v>
       </c>
       <c r="B198" s="32" t="s">
-        <v>1330</v>
+        <v>943</v>
       </c>
       <c r="C198" s="33" t="s">
-        <v>1331</v>
+        <v>1082</v>
       </c>
       <c r="D198" s="32" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="E198" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F198" s="34" t="s">
-        <v>1332</v>
+        <v>1083</v>
       </c>
       <c r="G198" s="32" t="s">
         <v>13</v>
@@ -17262,19 +17220,19 @@
         <v>663</v>
       </c>
       <c r="B199" s="32" t="s">
-        <v>1339</v>
+        <v>1097</v>
       </c>
       <c r="C199" s="33" t="s">
-        <v>1340</v>
+        <v>1098</v>
       </c>
       <c r="D199" s="32" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="E199" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F199" s="34" t="s">
-        <v>1341</v>
+        <v>1099</v>
       </c>
       <c r="G199" s="32" t="s">
         <v>13</v>
@@ -17283,7 +17241,7 @@
         <v>13</v>
       </c>
       <c r="I199" s="32" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J199" s="33" t="s">
         <v>13</v>
@@ -17295,7 +17253,7 @@
         <v>13</v>
       </c>
       <c r="M199" s="32" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N199" s="32" t="s">
         <v>13</v>
@@ -17320,65 +17278,65 @@
       </c>
     </row>
     <row r="200" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B200" s="29" t="s">
-        <v>1071</v>
-      </c>
-      <c r="C200" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="D200" s="29" t="s">
+      <c r="A200" s="32" t="s">
+        <v>663</v>
+      </c>
+      <c r="B200" s="32" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C200" s="33" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D200" s="32" t="s">
         <v>712</v>
       </c>
-      <c r="E200" s="30" t="s">
-        <v>1072</v>
-      </c>
-      <c r="F200" s="31" t="s">
-        <v>1073</v>
-      </c>
-      <c r="G200" s="29" t="s">
-        <v>713</v>
-      </c>
-      <c r="H200" s="29" t="s">
-        <v>669</v>
-      </c>
-      <c r="I200" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="J200" s="30" t="s">
-        <v>172</v>
-      </c>
-      <c r="K200" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="L200" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="M200" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="N200" s="29" t="s">
-        <v>1074</v>
-      </c>
-      <c r="O200" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="P200" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q200" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="R200" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="S200" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="T200" s="29" t="s">
-        <v>30</v>
+      <c r="E200" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F200" s="34" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G200" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H200" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="I200" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="J200" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="K200" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L200" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="M200" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="N200" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="O200" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="P200" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q200" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="R200" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="S200" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="T200" s="32" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="201" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17386,10 +17344,10 @@
         <v>663</v>
       </c>
       <c r="B201" s="32" t="s">
-        <v>1086</v>
+        <v>704</v>
       </c>
       <c r="C201" s="33" t="s">
-        <v>1087</v>
+        <v>1106</v>
       </c>
       <c r="D201" s="32" t="s">
         <v>712</v>
@@ -17398,7 +17356,7 @@
         <v>13</v>
       </c>
       <c r="F201" s="34" t="s">
-        <v>1088</v>
+        <v>1111</v>
       </c>
       <c r="G201" s="32" t="s">
         <v>13</v>
@@ -17448,10 +17406,10 @@
         <v>663</v>
       </c>
       <c r="B202" s="32" t="s">
-        <v>133</v>
+        <v>943</v>
       </c>
       <c r="C202" s="33" t="s">
-        <v>1090</v>
+        <v>1115</v>
       </c>
       <c r="D202" s="32" t="s">
         <v>712</v>
@@ -17460,7 +17418,7 @@
         <v>13</v>
       </c>
       <c r="F202" s="34" t="s">
-        <v>244</v>
+        <v>1116</v>
       </c>
       <c r="G202" s="32" t="s">
         <v>13</v>
@@ -17510,10 +17468,10 @@
         <v>663</v>
       </c>
       <c r="B203" s="32" t="s">
-        <v>943</v>
+        <v>1117</v>
       </c>
       <c r="C203" s="33" t="s">
-        <v>1096</v>
+        <v>1118</v>
       </c>
       <c r="D203" s="32" t="s">
         <v>712</v>
@@ -17522,7 +17480,7 @@
         <v>13</v>
       </c>
       <c r="F203" s="34" t="s">
-        <v>1097</v>
+        <v>1119</v>
       </c>
       <c r="G203" s="32" t="s">
         <v>13</v>
@@ -17572,10 +17530,10 @@
         <v>663</v>
       </c>
       <c r="B204" s="32" t="s">
-        <v>1111</v>
+        <v>1120</v>
       </c>
       <c r="C204" s="33" t="s">
-        <v>1112</v>
+        <v>1121</v>
       </c>
       <c r="D204" s="32" t="s">
         <v>712</v>
@@ -17584,7 +17542,7 @@
         <v>13</v>
       </c>
       <c r="F204" s="34" t="s">
-        <v>1113</v>
+        <v>1122</v>
       </c>
       <c r="G204" s="32" t="s">
         <v>13</v>
@@ -17593,7 +17551,7 @@
         <v>13</v>
       </c>
       <c r="I204" s="32" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J204" s="33" t="s">
         <v>13</v>
@@ -17605,7 +17563,7 @@
         <v>13</v>
       </c>
       <c r="M204" s="32" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N204" s="32" t="s">
         <v>13</v>
@@ -17634,10 +17592,10 @@
         <v>663</v>
       </c>
       <c r="B205" s="32" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
       <c r="C205" s="33" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="D205" s="32" t="s">
         <v>712</v>
@@ -17646,7 +17604,7 @@
         <v>13</v>
       </c>
       <c r="F205" s="34" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="G205" s="32" t="s">
         <v>13</v>
@@ -17696,10 +17654,10 @@
         <v>663</v>
       </c>
       <c r="B206" s="32" t="s">
-        <v>704</v>
+        <v>1124</v>
       </c>
       <c r="C206" s="33" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="D206" s="32" t="s">
         <v>712</v>
@@ -17708,7 +17666,7 @@
         <v>13</v>
       </c>
       <c r="F206" s="34" t="s">
-        <v>1125</v>
+        <v>735</v>
       </c>
       <c r="G206" s="32" t="s">
         <v>13</v>
@@ -17758,10 +17716,10 @@
         <v>663</v>
       </c>
       <c r="B207" s="32" t="s">
-        <v>943</v>
+        <v>1133</v>
       </c>
       <c r="C207" s="33" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
       <c r="D207" s="32" t="s">
         <v>712</v>
@@ -17770,7 +17728,7 @@
         <v>13</v>
       </c>
       <c r="F207" s="34" t="s">
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="G207" s="32" t="s">
         <v>13</v>
@@ -17820,10 +17778,10 @@
         <v>663</v>
       </c>
       <c r="B208" s="32" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="C208" s="33" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="D208" s="32" t="s">
         <v>712</v>
@@ -17832,7 +17790,7 @@
         <v>13</v>
       </c>
       <c r="F208" s="34" t="s">
-        <v>1133</v>
+        <v>1017</v>
       </c>
       <c r="G208" s="32" t="s">
         <v>13</v>
@@ -17882,10 +17840,10 @@
         <v>663</v>
       </c>
       <c r="B209" s="32" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C209" s="33" t="s">
         <v>1134</v>
-      </c>
-      <c r="C209" s="33" t="s">
-        <v>1135</v>
       </c>
       <c r="D209" s="32" t="s">
         <v>712</v>
@@ -17894,7 +17852,7 @@
         <v>13</v>
       </c>
       <c r="F209" s="34" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="G209" s="32" t="s">
         <v>13</v>
@@ -17944,10 +17902,10 @@
         <v>663</v>
       </c>
       <c r="B210" s="32" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="C210" s="33" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D210" s="32" t="s">
         <v>712</v>
@@ -17956,7 +17914,7 @@
         <v>13</v>
       </c>
       <c r="F210" s="34" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="G210" s="32" t="s">
         <v>13</v>
@@ -18006,10 +17964,10 @@
         <v>663</v>
       </c>
       <c r="B211" s="32" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="C211" s="33" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="D211" s="32" t="s">
         <v>712</v>
@@ -18018,7 +17976,7 @@
         <v>13</v>
       </c>
       <c r="F211" s="34" t="s">
-        <v>735</v>
+        <v>1143</v>
       </c>
       <c r="G211" s="32" t="s">
         <v>13</v>
@@ -18068,10 +18026,10 @@
         <v>663</v>
       </c>
       <c r="B212" s="32" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="C212" s="33" t="s">
-        <v>1148</v>
+        <v>1142</v>
       </c>
       <c r="D212" s="32" t="s">
         <v>712</v>
@@ -18080,7 +18038,7 @@
         <v>13</v>
       </c>
       <c r="F212" s="34" t="s">
-        <v>1149</v>
+        <v>1128</v>
       </c>
       <c r="G212" s="32" t="s">
         <v>13</v>
@@ -18130,10 +18088,10 @@
         <v>663</v>
       </c>
       <c r="B213" s="32" t="s">
-        <v>1150</v>
+        <v>1145</v>
       </c>
       <c r="C213" s="33" t="s">
-        <v>1148</v>
+        <v>1142</v>
       </c>
       <c r="D213" s="32" t="s">
         <v>712</v>
@@ -18142,7 +18100,7 @@
         <v>13</v>
       </c>
       <c r="F213" s="34" t="s">
-        <v>1017</v>
+        <v>1146</v>
       </c>
       <c r="G213" s="32" t="s">
         <v>13</v>
@@ -18192,10 +18150,10 @@
         <v>663</v>
       </c>
       <c r="B214" s="32" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="C214" s="33" t="s">
-        <v>1148</v>
+        <v>1142</v>
       </c>
       <c r="D214" s="32" t="s">
         <v>712</v>
@@ -18204,7 +18162,7 @@
         <v>13</v>
       </c>
       <c r="F214" s="34" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="G214" s="32" t="s">
         <v>13</v>
@@ -18254,10 +18212,10 @@
         <v>663</v>
       </c>
       <c r="B215" s="32" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="C215" s="33" t="s">
-        <v>1148</v>
+        <v>1142</v>
       </c>
       <c r="D215" s="32" t="s">
         <v>712</v>
@@ -18266,7 +18224,7 @@
         <v>13</v>
       </c>
       <c r="F215" s="34" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="G215" s="32" t="s">
         <v>13</v>
@@ -18316,10 +18274,10 @@
         <v>663</v>
       </c>
       <c r="B216" s="32" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="C216" s="33" t="s">
-        <v>1156</v>
+        <v>1142</v>
       </c>
       <c r="D216" s="32" t="s">
         <v>712</v>
@@ -18328,7 +18286,7 @@
         <v>13</v>
       </c>
       <c r="F216" s="34" t="s">
-        <v>1157</v>
+        <v>1095</v>
       </c>
       <c r="G216" s="32" t="s">
         <v>13</v>
@@ -18378,10 +18336,10 @@
         <v>663</v>
       </c>
       <c r="B217" s="32" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
       <c r="C217" s="33" t="s">
-        <v>1156</v>
+        <v>1142</v>
       </c>
       <c r="D217" s="32" t="s">
         <v>712</v>
@@ -18390,7 +18348,7 @@
         <v>13</v>
       </c>
       <c r="F217" s="34" t="s">
-        <v>1142</v>
+        <v>1153</v>
       </c>
       <c r="G217" s="32" t="s">
         <v>13</v>
@@ -18440,7 +18398,7 @@
         <v>663</v>
       </c>
       <c r="B218" s="32" t="s">
-        <v>1159</v>
+        <v>737</v>
       </c>
       <c r="C218" s="33" t="s">
         <v>1156</v>
@@ -18452,7 +18410,7 @@
         <v>13</v>
       </c>
       <c r="F218" s="34" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="G218" s="32" t="s">
         <v>13</v>
@@ -18502,7 +18460,7 @@
         <v>663</v>
       </c>
       <c r="B219" s="32" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="C219" s="33" t="s">
         <v>1156</v>
@@ -18514,7 +18472,7 @@
         <v>13</v>
       </c>
       <c r="F219" s="34" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="G219" s="32" t="s">
         <v>13</v>
@@ -18564,7 +18522,7 @@
         <v>663</v>
       </c>
       <c r="B220" s="32" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="C220" s="33" t="s">
         <v>1156</v>
@@ -18576,7 +18534,7 @@
         <v>13</v>
       </c>
       <c r="F220" s="34" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="G220" s="32" t="s">
         <v>13</v>
@@ -18626,7 +18584,7 @@
         <v>663</v>
       </c>
       <c r="B221" s="32" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="C221" s="33" t="s">
         <v>1156</v>
@@ -18638,7 +18596,7 @@
         <v>13</v>
       </c>
       <c r="F221" s="34" t="s">
-        <v>1109</v>
+        <v>1163</v>
       </c>
       <c r="G221" s="32" t="s">
         <v>13</v>
@@ -18688,10 +18646,10 @@
         <v>663</v>
       </c>
       <c r="B222" s="32" t="s">
-        <v>1166</v>
+        <v>738</v>
       </c>
       <c r="C222" s="33" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="D222" s="32" t="s">
         <v>712</v>
@@ -18700,7 +18658,7 @@
         <v>13</v>
       </c>
       <c r="F222" s="34" t="s">
-        <v>1167</v>
+        <v>389</v>
       </c>
       <c r="G222" s="32" t="s">
         <v>13</v>
@@ -18750,10 +18708,10 @@
         <v>663</v>
       </c>
       <c r="B223" s="32" t="s">
-        <v>737</v>
+        <v>1018</v>
       </c>
       <c r="C223" s="33" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="D223" s="32" t="s">
         <v>712</v>
@@ -18762,7 +18720,7 @@
         <v>13</v>
       </c>
       <c r="F223" s="34" t="s">
-        <v>1171</v>
+        <v>389</v>
       </c>
       <c r="G223" s="32" t="s">
         <v>13</v>
@@ -18812,10 +18770,10 @@
         <v>663</v>
       </c>
       <c r="B224" s="32" t="s">
-        <v>1172</v>
+        <v>801</v>
       </c>
       <c r="C224" s="33" t="s">
-        <v>1170</v>
+        <v>1175</v>
       </c>
       <c r="D224" s="32" t="s">
         <v>712</v>
@@ -18824,7 +18782,7 @@
         <v>13</v>
       </c>
       <c r="F224" s="34" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="G224" s="32" t="s">
         <v>13</v>
@@ -18874,10 +18832,10 @@
         <v>663</v>
       </c>
       <c r="B225" s="32" t="s">
-        <v>1174</v>
+        <v>1184</v>
       </c>
       <c r="C225" s="33" t="s">
-        <v>1170</v>
+        <v>1182</v>
       </c>
       <c r="D225" s="32" t="s">
         <v>712</v>
@@ -18886,7 +18844,7 @@
         <v>13</v>
       </c>
       <c r="F225" s="34" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="G225" s="32" t="s">
         <v>13</v>
@@ -18936,10 +18894,10 @@
         <v>663</v>
       </c>
       <c r="B226" s="32" t="s">
-        <v>1176</v>
+        <v>1185</v>
       </c>
       <c r="C226" s="33" t="s">
-        <v>1170</v>
+        <v>1182</v>
       </c>
       <c r="D226" s="32" t="s">
         <v>712</v>
@@ -18948,7 +18906,7 @@
         <v>13</v>
       </c>
       <c r="F226" s="34" t="s">
-        <v>1177</v>
+        <v>739</v>
       </c>
       <c r="G226" s="32" t="s">
         <v>13</v>
@@ -18998,10 +18956,10 @@
         <v>663</v>
       </c>
       <c r="B227" s="32" t="s">
-        <v>738</v>
+        <v>1186</v>
       </c>
       <c r="C227" s="33" t="s">
-        <v>1178</v>
+        <v>1187</v>
       </c>
       <c r="D227" s="32" t="s">
         <v>712</v>
@@ -19010,7 +18968,7 @@
         <v>13</v>
       </c>
       <c r="F227" s="34" t="s">
-        <v>389</v>
+        <v>1188</v>
       </c>
       <c r="G227" s="32" t="s">
         <v>13</v>
@@ -19060,10 +19018,10 @@
         <v>663</v>
       </c>
       <c r="B228" s="32" t="s">
-        <v>1018</v>
+        <v>1189</v>
       </c>
       <c r="C228" s="33" t="s">
-        <v>1178</v>
+        <v>1187</v>
       </c>
       <c r="D228" s="32" t="s">
         <v>712</v>
@@ -19072,7 +19030,7 @@
         <v>13</v>
       </c>
       <c r="F228" s="34" t="s">
-        <v>389</v>
+        <v>1190</v>
       </c>
       <c r="G228" s="32" t="s">
         <v>13</v>
@@ -19122,10 +19080,10 @@
         <v>663</v>
       </c>
       <c r="B229" s="32" t="s">
-        <v>801</v>
+        <v>1191</v>
       </c>
       <c r="C229" s="33" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="D229" s="32" t="s">
         <v>712</v>
@@ -19134,7 +19092,7 @@
         <v>13</v>
       </c>
       <c r="F229" s="34" t="s">
-        <v>1190</v>
+        <v>739</v>
       </c>
       <c r="G229" s="32" t="s">
         <v>13</v>
@@ -19184,10 +19142,10 @@
         <v>663</v>
       </c>
       <c r="B230" s="32" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="C230" s="33" t="s">
-        <v>1196</v>
+        <v>741</v>
       </c>
       <c r="D230" s="32" t="s">
         <v>712</v>
@@ -19196,7 +19154,7 @@
         <v>13</v>
       </c>
       <c r="F230" s="34" t="s">
-        <v>1188</v>
+        <v>1197</v>
       </c>
       <c r="G230" s="32" t="s">
         <v>13</v>
@@ -19246,10 +19204,10 @@
         <v>663</v>
       </c>
       <c r="B231" s="32" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C231" s="33" t="s">
-        <v>1196</v>
+        <v>741</v>
       </c>
       <c r="D231" s="32" t="s">
         <v>712</v>
@@ -19258,7 +19216,7 @@
         <v>13</v>
       </c>
       <c r="F231" s="34" t="s">
-        <v>739</v>
+        <v>1199</v>
       </c>
       <c r="G231" s="32" t="s">
         <v>13</v>
@@ -19308,10 +19266,10 @@
         <v>663</v>
       </c>
       <c r="B232" s="32" t="s">
-        <v>1200</v>
+        <v>1080</v>
       </c>
       <c r="C232" s="33" t="s">
-        <v>1201</v>
+        <v>1216</v>
       </c>
       <c r="D232" s="32" t="s">
         <v>712</v>
@@ -19320,7 +19278,7 @@
         <v>13</v>
       </c>
       <c r="F232" s="34" t="s">
-        <v>1202</v>
+        <v>1217</v>
       </c>
       <c r="G232" s="32" t="s">
         <v>13</v>
@@ -19370,10 +19328,10 @@
         <v>663</v>
       </c>
       <c r="B233" s="32" t="s">
-        <v>1203</v>
+        <v>1218</v>
       </c>
       <c r="C233" s="33" t="s">
-        <v>1201</v>
+        <v>1216</v>
       </c>
       <c r="D233" s="32" t="s">
         <v>712</v>
@@ -19382,7 +19340,7 @@
         <v>13</v>
       </c>
       <c r="F233" s="34" t="s">
-        <v>1204</v>
+        <v>1219</v>
       </c>
       <c r="G233" s="32" t="s">
         <v>13</v>
@@ -19432,10 +19390,10 @@
         <v>663</v>
       </c>
       <c r="B234" s="32" t="s">
-        <v>1205</v>
+        <v>1117</v>
       </c>
       <c r="C234" s="33" t="s">
-        <v>1201</v>
+        <v>1216</v>
       </c>
       <c r="D234" s="32" t="s">
         <v>712</v>
@@ -19444,7 +19402,7 @@
         <v>13</v>
       </c>
       <c r="F234" s="34" t="s">
-        <v>739</v>
+        <v>1220</v>
       </c>
       <c r="G234" s="32" t="s">
         <v>13</v>
@@ -19494,10 +19452,10 @@
         <v>663</v>
       </c>
       <c r="B235" s="32" t="s">
-        <v>1210</v>
+        <v>730</v>
       </c>
       <c r="C235" s="33" t="s">
-        <v>741</v>
+        <v>1216</v>
       </c>
       <c r="D235" s="32" t="s">
         <v>712</v>
@@ -19506,7 +19464,7 @@
         <v>13</v>
       </c>
       <c r="F235" s="34" t="s">
-        <v>1211</v>
+        <v>749</v>
       </c>
       <c r="G235" s="32" t="s">
         <v>13</v>
@@ -19556,10 +19514,10 @@
         <v>663</v>
       </c>
       <c r="B236" s="32" t="s">
-        <v>1212</v>
+        <v>1221</v>
       </c>
       <c r="C236" s="33" t="s">
-        <v>741</v>
+        <v>1216</v>
       </c>
       <c r="D236" s="32" t="s">
         <v>712</v>
@@ -19568,7 +19526,7 @@
         <v>13</v>
       </c>
       <c r="F236" s="34" t="s">
-        <v>1213</v>
+        <v>1222</v>
       </c>
       <c r="G236" s="32" t="s">
         <v>13</v>
@@ -19618,10 +19576,10 @@
         <v>663</v>
       </c>
       <c r="B237" s="32" t="s">
-        <v>1094</v>
+        <v>1168</v>
       </c>
       <c r="C237" s="33" t="s">
-        <v>1230</v>
+        <v>751</v>
       </c>
       <c r="D237" s="32" t="s">
         <v>712</v>
@@ -19630,7 +19588,7 @@
         <v>13</v>
       </c>
       <c r="F237" s="34" t="s">
-        <v>1231</v>
+        <v>1001</v>
       </c>
       <c r="G237" s="32" t="s">
         <v>13</v>
@@ -19680,10 +19638,10 @@
         <v>663</v>
       </c>
       <c r="B238" s="32" t="s">
-        <v>1232</v>
+        <v>1169</v>
       </c>
       <c r="C238" s="33" t="s">
-        <v>1230</v>
+        <v>751</v>
       </c>
       <c r="D238" s="32" t="s">
         <v>712</v>
@@ -19692,7 +19650,7 @@
         <v>13</v>
       </c>
       <c r="F238" s="34" t="s">
-        <v>1233</v>
+        <v>1128</v>
       </c>
       <c r="G238" s="32" t="s">
         <v>13</v>
@@ -19742,10 +19700,10 @@
         <v>663</v>
       </c>
       <c r="B239" s="32" t="s">
-        <v>1131</v>
+        <v>138</v>
       </c>
       <c r="C239" s="33" t="s">
-        <v>1230</v>
+        <v>1243</v>
       </c>
       <c r="D239" s="32" t="s">
         <v>712</v>
@@ -19754,7 +19712,7 @@
         <v>13</v>
       </c>
       <c r="F239" s="34" t="s">
-        <v>1234</v>
+        <v>753</v>
       </c>
       <c r="G239" s="32" t="s">
         <v>13</v>
@@ -19804,10 +19762,10 @@
         <v>663</v>
       </c>
       <c r="B240" s="32" t="s">
-        <v>730</v>
+        <v>1186</v>
       </c>
       <c r="C240" s="33" t="s">
-        <v>1230</v>
+        <v>1244</v>
       </c>
       <c r="D240" s="32" t="s">
         <v>712</v>
@@ -19816,7 +19774,7 @@
         <v>13</v>
       </c>
       <c r="F240" s="34" t="s">
-        <v>749</v>
+        <v>1245</v>
       </c>
       <c r="G240" s="32" t="s">
         <v>13</v>
@@ -19866,10 +19824,10 @@
         <v>663</v>
       </c>
       <c r="B241" s="32" t="s">
-        <v>1235</v>
+        <v>1124</v>
       </c>
       <c r="C241" s="33" t="s">
-        <v>1230</v>
+        <v>1248</v>
       </c>
       <c r="D241" s="32" t="s">
         <v>712</v>
@@ -19878,7 +19836,7 @@
         <v>13</v>
       </c>
       <c r="F241" s="34" t="s">
-        <v>1236</v>
+        <v>1249</v>
       </c>
       <c r="G241" s="32" t="s">
         <v>13</v>
@@ -19928,10 +19886,10 @@
         <v>663</v>
       </c>
       <c r="B242" s="32" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="C242" s="33" t="s">
-        <v>751</v>
+        <v>1281</v>
       </c>
       <c r="D242" s="32" t="s">
         <v>712</v>
@@ -19940,7 +19898,7 @@
         <v>13</v>
       </c>
       <c r="F242" s="34" t="s">
-        <v>1001</v>
+        <v>1282</v>
       </c>
       <c r="G242" s="32" t="s">
         <v>13</v>
@@ -19990,10 +19948,10 @@
         <v>663</v>
       </c>
       <c r="B243" s="32" t="s">
-        <v>1183</v>
+        <v>1013</v>
       </c>
       <c r="C243" s="33" t="s">
-        <v>751</v>
+        <v>1286</v>
       </c>
       <c r="D243" s="32" t="s">
         <v>712</v>
@@ -20002,7 +19960,7 @@
         <v>13</v>
       </c>
       <c r="F243" s="34" t="s">
-        <v>1142</v>
+        <v>1287</v>
       </c>
       <c r="G243" s="32" t="s">
         <v>13</v>
@@ -20052,10 +20010,10 @@
         <v>663</v>
       </c>
       <c r="B244" s="32" t="s">
-        <v>138</v>
+        <v>1231</v>
       </c>
       <c r="C244" s="33" t="s">
-        <v>1257</v>
+        <v>1296</v>
       </c>
       <c r="D244" s="32" t="s">
         <v>712</v>
@@ -20064,7 +20022,7 @@
         <v>13</v>
       </c>
       <c r="F244" s="34" t="s">
-        <v>753</v>
+        <v>1297</v>
       </c>
       <c r="G244" s="32" t="s">
         <v>13</v>
@@ -20114,10 +20072,10 @@
         <v>663</v>
       </c>
       <c r="B245" s="32" t="s">
-        <v>1200</v>
+        <v>1298</v>
       </c>
       <c r="C245" s="33" t="s">
-        <v>1258</v>
+        <v>1299</v>
       </c>
       <c r="D245" s="32" t="s">
         <v>712</v>
@@ -20126,7 +20084,7 @@
         <v>13</v>
       </c>
       <c r="F245" s="34" t="s">
-        <v>1259</v>
+        <v>93</v>
       </c>
       <c r="G245" s="32" t="s">
         <v>13</v>
@@ -20176,10 +20134,10 @@
         <v>663</v>
       </c>
       <c r="B246" s="32" t="s">
-        <v>1138</v>
+        <v>1300</v>
       </c>
       <c r="C246" s="33" t="s">
-        <v>1262</v>
+        <v>1299</v>
       </c>
       <c r="D246" s="32" t="s">
         <v>712</v>
@@ -20188,7 +20146,7 @@
         <v>13</v>
       </c>
       <c r="F246" s="34" t="s">
-        <v>1263</v>
+        <v>93</v>
       </c>
       <c r="G246" s="32" t="s">
         <v>13</v>
@@ -20238,10 +20196,10 @@
         <v>663</v>
       </c>
       <c r="B247" s="32" t="s">
-        <v>1200</v>
+        <v>1301</v>
       </c>
       <c r="C247" s="33" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="D247" s="32" t="s">
         <v>712</v>
@@ -20250,7 +20208,7 @@
         <v>13</v>
       </c>
       <c r="F247" s="34" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
       <c r="G247" s="32" t="s">
         <v>13</v>
@@ -20300,10 +20258,10 @@
         <v>663</v>
       </c>
       <c r="B248" s="32" t="s">
-        <v>1013</v>
+        <v>1307</v>
       </c>
       <c r="C248" s="33" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="D248" s="32" t="s">
         <v>712</v>
@@ -20312,7 +20270,7 @@
         <v>13</v>
       </c>
       <c r="F248" s="34" t="s">
-        <v>1301</v>
+        <v>1308</v>
       </c>
       <c r="G248" s="32" t="s">
         <v>13</v>
@@ -20362,7 +20320,7 @@
         <v>663</v>
       </c>
       <c r="B249" s="32" t="s">
-        <v>1245</v>
+        <v>1309</v>
       </c>
       <c r="C249" s="33" t="s">
         <v>1310</v>
@@ -20424,10 +20382,10 @@
         <v>663</v>
       </c>
       <c r="B250" s="32" t="s">
-        <v>1312</v>
+        <v>1319</v>
       </c>
       <c r="C250" s="33" t="s">
-        <v>1313</v>
+        <v>1320</v>
       </c>
       <c r="D250" s="32" t="s">
         <v>712</v>
@@ -20436,7 +20394,7 @@
         <v>13</v>
       </c>
       <c r="F250" s="34" t="s">
-        <v>93</v>
+        <v>1321</v>
       </c>
       <c r="G250" s="32" t="s">
         <v>13</v>
@@ -20486,10 +20444,10 @@
         <v>663</v>
       </c>
       <c r="B251" s="32" t="s">
-        <v>1314</v>
+        <v>1322</v>
       </c>
       <c r="C251" s="33" t="s">
-        <v>1313</v>
+        <v>1323</v>
       </c>
       <c r="D251" s="32" t="s">
         <v>712</v>
@@ -20498,7 +20456,7 @@
         <v>13</v>
       </c>
       <c r="F251" s="34" t="s">
-        <v>93</v>
+        <v>1324</v>
       </c>
       <c r="G251" s="32" t="s">
         <v>13</v>
@@ -20548,10 +20506,10 @@
         <v>663</v>
       </c>
       <c r="B252" s="32" t="s">
-        <v>1315</v>
+        <v>1332</v>
       </c>
       <c r="C252" s="33" t="s">
-        <v>1313</v>
+        <v>1333</v>
       </c>
       <c r="D252" s="32" t="s">
         <v>712</v>
@@ -20560,7 +20518,7 @@
         <v>13</v>
       </c>
       <c r="F252" s="34" t="s">
-        <v>1316</v>
+        <v>1334</v>
       </c>
       <c r="G252" s="32" t="s">
         <v>13</v>
@@ -20610,10 +20568,10 @@
         <v>663</v>
       </c>
       <c r="B253" s="32" t="s">
-        <v>1321</v>
+        <v>1335</v>
       </c>
       <c r="C253" s="33" t="s">
-        <v>1318</v>
+        <v>1333</v>
       </c>
       <c r="D253" s="32" t="s">
         <v>712</v>
@@ -20622,7 +20580,7 @@
         <v>13</v>
       </c>
       <c r="F253" s="34" t="s">
-        <v>1322</v>
+        <v>1336</v>
       </c>
       <c r="G253" s="32" t="s">
         <v>13</v>
@@ -20672,10 +20630,10 @@
         <v>663</v>
       </c>
       <c r="B254" s="32" t="s">
-        <v>1323</v>
+        <v>1337</v>
       </c>
       <c r="C254" s="33" t="s">
-        <v>1324</v>
+        <v>1333</v>
       </c>
       <c r="D254" s="32" t="s">
         <v>712</v>
@@ -20684,7 +20642,7 @@
         <v>13</v>
       </c>
       <c r="F254" s="34" t="s">
-        <v>1325</v>
+        <v>1338</v>
       </c>
       <c r="G254" s="32" t="s">
         <v>13</v>
@@ -20734,10 +20692,10 @@
         <v>663</v>
       </c>
       <c r="B255" s="32" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C255" s="33" t="s">
         <v>1333</v>
-      </c>
-      <c r="C255" s="33" t="s">
-        <v>1334</v>
       </c>
       <c r="D255" s="32" t="s">
         <v>712</v>
@@ -20746,7 +20704,7 @@
         <v>13</v>
       </c>
       <c r="F255" s="34" t="s">
-        <v>1335</v>
+        <v>1340</v>
       </c>
       <c r="G255" s="32" t="s">
         <v>13</v>
@@ -20796,10 +20754,10 @@
         <v>663</v>
       </c>
       <c r="B256" s="32" t="s">
-        <v>1336</v>
+        <v>1344</v>
       </c>
       <c r="C256" s="33" t="s">
-        <v>1337</v>
+        <v>791</v>
       </c>
       <c r="D256" s="32" t="s">
         <v>712</v>
@@ -20808,7 +20766,7 @@
         <v>13</v>
       </c>
       <c r="F256" s="34" t="s">
-        <v>1338</v>
+        <v>1345</v>
       </c>
       <c r="G256" s="32" t="s">
         <v>13</v>
@@ -20817,7 +20775,7 @@
         <v>13</v>
       </c>
       <c r="I256" s="32" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="J256" s="33" t="s">
         <v>13</v>
@@ -20829,7 +20787,7 @@
         <v>13</v>
       </c>
       <c r="M256" s="32" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="N256" s="32" t="s">
         <v>13</v>
@@ -20858,19 +20816,19 @@
         <v>663</v>
       </c>
       <c r="B257" s="32" t="s">
-        <v>1346</v>
+        <v>1077</v>
       </c>
       <c r="C257" s="33" t="s">
-        <v>1347</v>
+        <v>1078</v>
       </c>
       <c r="D257" s="32" t="s">
-        <v>712</v>
+        <v>638</v>
       </c>
       <c r="E257" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F257" s="34" t="s">
-        <v>1348</v>
+        <v>1079</v>
       </c>
       <c r="G257" s="32" t="s">
         <v>13</v>
@@ -20920,19 +20878,19 @@
         <v>663</v>
       </c>
       <c r="B258" s="32" t="s">
-        <v>1349</v>
+        <v>1080</v>
       </c>
       <c r="C258" s="33" t="s">
-        <v>1347</v>
+        <v>1078</v>
       </c>
       <c r="D258" s="32" t="s">
-        <v>712</v>
+        <v>638</v>
       </c>
       <c r="E258" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F258" s="34" t="s">
-        <v>1350</v>
+        <v>1081</v>
       </c>
       <c r="G258" s="32" t="s">
         <v>13</v>
@@ -20982,19 +20940,19 @@
         <v>663</v>
       </c>
       <c r="B259" s="32" t="s">
-        <v>1351</v>
+        <v>1234</v>
       </c>
       <c r="C259" s="33" t="s">
-        <v>1347</v>
+        <v>1232</v>
       </c>
       <c r="D259" s="32" t="s">
-        <v>712</v>
+        <v>638</v>
       </c>
       <c r="E259" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F259" s="34" t="s">
-        <v>1352</v>
+        <v>1233</v>
       </c>
       <c r="G259" s="32" t="s">
         <v>13</v>
@@ -21044,19 +21002,19 @@
         <v>663</v>
       </c>
       <c r="B260" s="32" t="s">
-        <v>1353</v>
+        <v>1235</v>
       </c>
       <c r="C260" s="33" t="s">
-        <v>1347</v>
+        <v>1232</v>
       </c>
       <c r="D260" s="32" t="s">
-        <v>712</v>
+        <v>638</v>
       </c>
       <c r="E260" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F260" s="34" t="s">
-        <v>1354</v>
+        <v>1233</v>
       </c>
       <c r="G260" s="32" t="s">
         <v>13</v>
@@ -21106,19 +21064,19 @@
         <v>663</v>
       </c>
       <c r="B261" s="32" t="s">
-        <v>1358</v>
+        <v>1236</v>
       </c>
       <c r="C261" s="33" t="s">
-        <v>791</v>
+        <v>1232</v>
       </c>
       <c r="D261" s="32" t="s">
-        <v>712</v>
+        <v>638</v>
       </c>
       <c r="E261" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F261" s="34" t="s">
-        <v>1359</v>
+        <v>1233</v>
       </c>
       <c r="G261" s="32" t="s">
         <v>13</v>
@@ -21127,7 +21085,7 @@
         <v>13</v>
       </c>
       <c r="I261" s="32" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J261" s="33" t="s">
         <v>13</v>
@@ -21139,7 +21097,7 @@
         <v>13</v>
       </c>
       <c r="M261" s="32" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="N261" s="32" t="s">
         <v>13</v>
@@ -21168,10 +21126,10 @@
         <v>663</v>
       </c>
       <c r="B262" s="32" t="s">
-        <v>1091</v>
+        <v>1237</v>
       </c>
       <c r="C262" s="33" t="s">
-        <v>1092</v>
+        <v>1232</v>
       </c>
       <c r="D262" s="32" t="s">
         <v>638</v>
@@ -21180,7 +21138,7 @@
         <v>13</v>
       </c>
       <c r="F262" s="34" t="s">
-        <v>1093</v>
+        <v>1233</v>
       </c>
       <c r="G262" s="32" t="s">
         <v>13</v>
@@ -21230,10 +21188,10 @@
         <v>663</v>
       </c>
       <c r="B263" s="32" t="s">
-        <v>1094</v>
+        <v>1238</v>
       </c>
       <c r="C263" s="33" t="s">
-        <v>1092</v>
+        <v>1232</v>
       </c>
       <c r="D263" s="32" t="s">
         <v>638</v>
@@ -21242,7 +21200,7 @@
         <v>13</v>
       </c>
       <c r="F263" s="34" t="s">
-        <v>1095</v>
+        <v>1233</v>
       </c>
       <c r="G263" s="32" t="s">
         <v>13</v>
@@ -21292,10 +21250,10 @@
         <v>663</v>
       </c>
       <c r="B264" s="32" t="s">
-        <v>1248</v>
+        <v>1239</v>
       </c>
       <c r="C264" s="33" t="s">
-        <v>1246</v>
+        <v>1232</v>
       </c>
       <c r="D264" s="32" t="s">
         <v>638</v>
@@ -21304,7 +21262,7 @@
         <v>13</v>
       </c>
       <c r="F264" s="34" t="s">
-        <v>1247</v>
+        <v>1233</v>
       </c>
       <c r="G264" s="32" t="s">
         <v>13</v>
@@ -21354,10 +21312,10 @@
         <v>663</v>
       </c>
       <c r="B265" s="32" t="s">
-        <v>1249</v>
+        <v>1240</v>
       </c>
       <c r="C265" s="33" t="s">
-        <v>1246</v>
+        <v>1232</v>
       </c>
       <c r="D265" s="32" t="s">
         <v>638</v>
@@ -21366,7 +21324,7 @@
         <v>13</v>
       </c>
       <c r="F265" s="34" t="s">
-        <v>1247</v>
+        <v>1233</v>
       </c>
       <c r="G265" s="32" t="s">
         <v>13</v>
@@ -21416,10 +21374,10 @@
         <v>663</v>
       </c>
       <c r="B266" s="32" t="s">
-        <v>1250</v>
+        <v>1261</v>
       </c>
       <c r="C266" s="33" t="s">
-        <v>1246</v>
+        <v>1262</v>
       </c>
       <c r="D266" s="32" t="s">
         <v>638</v>
@@ -21428,7 +21386,7 @@
         <v>13</v>
       </c>
       <c r="F266" s="34" t="s">
-        <v>1247</v>
+        <v>1263</v>
       </c>
       <c r="G266" s="32" t="s">
         <v>13</v>
@@ -21458,7 +21416,7 @@
         <v>13</v>
       </c>
       <c r="P266" s="33" t="s">
-        <v>13</v>
+        <v>1399</v>
       </c>
       <c r="Q266" s="33" t="s">
         <v>13</v>
@@ -21478,10 +21436,10 @@
         <v>663</v>
       </c>
       <c r="B267" s="32" t="s">
-        <v>1251</v>
+        <v>1264</v>
       </c>
       <c r="C267" s="33" t="s">
-        <v>1246</v>
+        <v>1262</v>
       </c>
       <c r="D267" s="32" t="s">
         <v>638</v>
@@ -21490,7 +21448,7 @@
         <v>13</v>
       </c>
       <c r="F267" s="34" t="s">
-        <v>1247</v>
+        <v>1265</v>
       </c>
       <c r="G267" s="32" t="s">
         <v>13</v>
@@ -21520,7 +21478,7 @@
         <v>13</v>
       </c>
       <c r="P267" s="33" t="s">
-        <v>13</v>
+        <v>1399</v>
       </c>
       <c r="Q267" s="33" t="s">
         <v>13</v>
@@ -21540,10 +21498,10 @@
         <v>663</v>
       </c>
       <c r="B268" s="32" t="s">
-        <v>1252</v>
+        <v>1266</v>
       </c>
       <c r="C268" s="33" t="s">
-        <v>1246</v>
+        <v>1262</v>
       </c>
       <c r="D268" s="32" t="s">
         <v>638</v>
@@ -21552,7 +21510,7 @@
         <v>13</v>
       </c>
       <c r="F268" s="34" t="s">
-        <v>1247</v>
+        <v>1267</v>
       </c>
       <c r="G268" s="32" t="s">
         <v>13</v>
@@ -21561,7 +21519,7 @@
         <v>13</v>
       </c>
       <c r="I268" s="32" t="s">
-        <v>13</v>
+        <v>266</v>
       </c>
       <c r="J268" s="33" t="s">
         <v>13</v>
@@ -21573,7 +21531,7 @@
         <v>13</v>
       </c>
       <c r="M268" s="32" t="s">
-        <v>13</v>
+        <v>266</v>
       </c>
       <c r="N268" s="32" t="s">
         <v>13</v>
@@ -21582,7 +21540,7 @@
         <v>13</v>
       </c>
       <c r="P268" s="33" t="s">
-        <v>13</v>
+        <v>1399</v>
       </c>
       <c r="Q268" s="33" t="s">
         <v>13</v>
@@ -21602,10 +21560,10 @@
         <v>663</v>
       </c>
       <c r="B269" s="32" t="s">
-        <v>1253</v>
+        <v>1268</v>
       </c>
       <c r="C269" s="33" t="s">
-        <v>1246</v>
+        <v>1262</v>
       </c>
       <c r="D269" s="32" t="s">
         <v>638</v>
@@ -21614,7 +21572,7 @@
         <v>13</v>
       </c>
       <c r="F269" s="34" t="s">
-        <v>1247</v>
+        <v>1269</v>
       </c>
       <c r="G269" s="32" t="s">
         <v>13</v>
@@ -21623,7 +21581,7 @@
         <v>13</v>
       </c>
       <c r="I269" s="32" t="s">
-        <v>13</v>
+        <v>266</v>
       </c>
       <c r="J269" s="33" t="s">
         <v>13</v>
@@ -21635,7 +21593,7 @@
         <v>13</v>
       </c>
       <c r="M269" s="32" t="s">
-        <v>13</v>
+        <v>266</v>
       </c>
       <c r="N269" s="32" t="s">
         <v>13</v>
@@ -21644,7 +21602,7 @@
         <v>13</v>
       </c>
       <c r="P269" s="33" t="s">
-        <v>13</v>
+        <v>1399</v>
       </c>
       <c r="Q269" s="33" t="s">
         <v>13</v>
@@ -21664,10 +21622,10 @@
         <v>663</v>
       </c>
       <c r="B270" s="32" t="s">
-        <v>1254</v>
+        <v>1270</v>
       </c>
       <c r="C270" s="33" t="s">
-        <v>1246</v>
+        <v>1262</v>
       </c>
       <c r="D270" s="32" t="s">
         <v>638</v>
@@ -21676,7 +21634,7 @@
         <v>13</v>
       </c>
       <c r="F270" s="34" t="s">
-        <v>1247</v>
+        <v>1269</v>
       </c>
       <c r="G270" s="32" t="s">
         <v>13</v>
@@ -21685,7 +21643,7 @@
         <v>13</v>
       </c>
       <c r="I270" s="32" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="J270" s="33" t="s">
         <v>13</v>
@@ -21697,7 +21655,7 @@
         <v>13</v>
       </c>
       <c r="M270" s="32" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="N270" s="32" t="s">
         <v>13</v>
@@ -21706,7 +21664,7 @@
         <v>13</v>
       </c>
       <c r="P270" s="33" t="s">
-        <v>13</v>
+        <v>1399</v>
       </c>
       <c r="Q270" s="33" t="s">
         <v>13</v>
@@ -21726,10 +21684,10 @@
         <v>663</v>
       </c>
       <c r="B271" s="32" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="C271" s="33" t="s">
-        <v>1276</v>
+        <v>1262</v>
       </c>
       <c r="D271" s="32" t="s">
         <v>638</v>
@@ -21738,7 +21696,7 @@
         <v>13</v>
       </c>
       <c r="F271" s="34" t="s">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="G271" s="32" t="s">
         <v>13</v>
@@ -21747,7 +21705,7 @@
         <v>13</v>
       </c>
       <c r="I271" s="32" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="J271" s="33" t="s">
         <v>13</v>
@@ -21759,7 +21717,7 @@
         <v>13</v>
       </c>
       <c r="M271" s="32" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="N271" s="32" t="s">
         <v>13</v>
@@ -21768,7 +21726,7 @@
         <v>13</v>
       </c>
       <c r="P271" s="33" t="s">
-        <v>1413</v>
+        <v>1399</v>
       </c>
       <c r="Q271" s="33" t="s">
         <v>13</v>
@@ -21788,10 +21746,10 @@
         <v>663</v>
       </c>
       <c r="B272" s="32" t="s">
-        <v>1278</v>
+        <v>1273</v>
       </c>
       <c r="C272" s="33" t="s">
-        <v>1276</v>
+        <v>1262</v>
       </c>
       <c r="D272" s="32" t="s">
         <v>638</v>
@@ -21800,7 +21758,7 @@
         <v>13</v>
       </c>
       <c r="F272" s="34" t="s">
-        <v>1279</v>
+        <v>1274</v>
       </c>
       <c r="G272" s="32" t="s">
         <v>13</v>
@@ -21809,7 +21767,7 @@
         <v>13</v>
       </c>
       <c r="I272" s="32" t="s">
-        <v>13</v>
+        <v>1275</v>
       </c>
       <c r="J272" s="33" t="s">
         <v>13</v>
@@ -21821,7 +21779,7 @@
         <v>13</v>
       </c>
       <c r="M272" s="32" t="s">
-        <v>13</v>
+        <v>1275</v>
       </c>
       <c r="N272" s="32" t="s">
         <v>13</v>
@@ -21830,7 +21788,7 @@
         <v>13</v>
       </c>
       <c r="P272" s="33" t="s">
-        <v>1413</v>
+        <v>1399</v>
       </c>
       <c r="Q272" s="33" t="s">
         <v>13</v>
@@ -21850,10 +21808,10 @@
         <v>663</v>
       </c>
       <c r="B273" s="32" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="C273" s="33" t="s">
-        <v>1276</v>
+        <v>1262</v>
       </c>
       <c r="D273" s="32" t="s">
         <v>638</v>
@@ -21862,7 +21820,7 @@
         <v>13</v>
       </c>
       <c r="F273" s="34" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="G273" s="32" t="s">
         <v>13</v>
@@ -21871,7 +21829,7 @@
         <v>13</v>
       </c>
       <c r="I273" s="32" t="s">
-        <v>266</v>
+        <v>16</v>
       </c>
       <c r="J273" s="33" t="s">
         <v>13</v>
@@ -21883,7 +21841,7 @@
         <v>13</v>
       </c>
       <c r="M273" s="32" t="s">
-        <v>266</v>
+        <v>16</v>
       </c>
       <c r="N273" s="32" t="s">
         <v>13</v>
@@ -21892,7 +21850,7 @@
         <v>13</v>
       </c>
       <c r="P273" s="33" t="s">
-        <v>1413</v>
+        <v>1399</v>
       </c>
       <c r="Q273" s="33" t="s">
         <v>13</v>
@@ -21912,10 +21870,10 @@
         <v>663</v>
       </c>
       <c r="B274" s="32" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="C274" s="33" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="D274" s="32" t="s">
         <v>638</v>
@@ -21924,7 +21882,7 @@
         <v>13</v>
       </c>
       <c r="F274" s="34" t="s">
-        <v>1283</v>
+        <v>763</v>
       </c>
       <c r="G274" s="32" t="s">
         <v>13</v>
@@ -21933,7 +21891,7 @@
         <v>13</v>
       </c>
       <c r="I274" s="32" t="s">
-        <v>266</v>
+        <v>13</v>
       </c>
       <c r="J274" s="33" t="s">
         <v>13</v>
@@ -21945,7 +21903,7 @@
         <v>13</v>
       </c>
       <c r="M274" s="32" t="s">
-        <v>266</v>
+        <v>13</v>
       </c>
       <c r="N274" s="32" t="s">
         <v>13</v>
@@ -21954,7 +21912,7 @@
         <v>13</v>
       </c>
       <c r="P274" s="33" t="s">
-        <v>1413</v>
+        <v>1399</v>
       </c>
       <c r="Q274" s="33" t="s">
         <v>13</v>
@@ -21974,19 +21932,19 @@
         <v>663</v>
       </c>
       <c r="B275" s="32" t="s">
-        <v>1284</v>
+        <v>1346</v>
       </c>
       <c r="C275" s="33" t="s">
-        <v>1276</v>
+        <v>802</v>
       </c>
       <c r="D275" s="32" t="s">
-        <v>638</v>
+        <v>653</v>
       </c>
       <c r="E275" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F275" s="34" t="s">
-        <v>1283</v>
+        <v>1347</v>
       </c>
       <c r="G275" s="32" t="s">
         <v>13</v>
@@ -21995,7 +21953,7 @@
         <v>13</v>
       </c>
       <c r="I275" s="32" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J275" s="33" t="s">
         <v>13</v>
@@ -22007,7 +21965,7 @@
         <v>13</v>
       </c>
       <c r="M275" s="32" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="N275" s="32" t="s">
         <v>13</v>
@@ -22016,7 +21974,7 @@
         <v>13</v>
       </c>
       <c r="P275" s="33" t="s">
-        <v>1413</v>
+        <v>17</v>
       </c>
       <c r="Q275" s="33" t="s">
         <v>13</v>
@@ -22036,19 +21994,19 @@
         <v>663</v>
       </c>
       <c r="B276" s="32" t="s">
-        <v>1285</v>
+        <v>1348</v>
       </c>
       <c r="C276" s="33" t="s">
-        <v>1276</v>
+        <v>802</v>
       </c>
       <c r="D276" s="32" t="s">
-        <v>638</v>
+        <v>653</v>
       </c>
       <c r="E276" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F276" s="34" t="s">
-        <v>1286</v>
+        <v>1349</v>
       </c>
       <c r="G276" s="32" t="s">
         <v>13</v>
@@ -22057,7 +22015,7 @@
         <v>13</v>
       </c>
       <c r="I276" s="32" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J276" s="33" t="s">
         <v>13</v>
@@ -22069,7 +22027,7 @@
         <v>13</v>
       </c>
       <c r="M276" s="32" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="N276" s="32" t="s">
         <v>13</v>
@@ -22078,7 +22036,7 @@
         <v>13</v>
       </c>
       <c r="P276" s="33" t="s">
-        <v>1413</v>
+        <v>17</v>
       </c>
       <c r="Q276" s="33" t="s">
         <v>13</v>
@@ -22098,19 +22056,19 @@
         <v>663</v>
       </c>
       <c r="B277" s="32" t="s">
-        <v>1287</v>
+        <v>1350</v>
       </c>
       <c r="C277" s="33" t="s">
-        <v>1276</v>
+        <v>802</v>
       </c>
       <c r="D277" s="32" t="s">
-        <v>638</v>
+        <v>653</v>
       </c>
       <c r="E277" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F277" s="34" t="s">
-        <v>1288</v>
+        <v>1351</v>
       </c>
       <c r="G277" s="32" t="s">
         <v>13</v>
@@ -22119,7 +22077,7 @@
         <v>13</v>
       </c>
       <c r="I277" s="32" t="s">
-        <v>1289</v>
+        <v>13</v>
       </c>
       <c r="J277" s="33" t="s">
         <v>13</v>
@@ -22131,7 +22089,7 @@
         <v>13</v>
       </c>
       <c r="M277" s="32" t="s">
-        <v>1289</v>
+        <v>13</v>
       </c>
       <c r="N277" s="32" t="s">
         <v>13</v>
@@ -22140,7 +22098,7 @@
         <v>13</v>
       </c>
       <c r="P277" s="33" t="s">
-        <v>1413</v>
+        <v>17</v>
       </c>
       <c r="Q277" s="33" t="s">
         <v>13</v>
@@ -22160,19 +22118,19 @@
         <v>663</v>
       </c>
       <c r="B278" s="32" t="s">
-        <v>1290</v>
+        <v>1352</v>
       </c>
       <c r="C278" s="33" t="s">
-        <v>1276</v>
+        <v>802</v>
       </c>
       <c r="D278" s="32" t="s">
-        <v>638</v>
+        <v>653</v>
       </c>
       <c r="E278" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F278" s="34" t="s">
-        <v>1291</v>
+        <v>1353</v>
       </c>
       <c r="G278" s="32" t="s">
         <v>13</v>
@@ -22181,7 +22139,7 @@
         <v>13</v>
       </c>
       <c r="I278" s="32" t="s">
-        <v>16</v>
+        <v>266</v>
       </c>
       <c r="J278" s="33" t="s">
         <v>13</v>
@@ -22193,7 +22151,7 @@
         <v>13</v>
       </c>
       <c r="M278" s="32" t="s">
-        <v>16</v>
+        <v>266</v>
       </c>
       <c r="N278" s="32" t="s">
         <v>13</v>
@@ -22202,7 +22160,7 @@
         <v>13</v>
       </c>
       <c r="P278" s="33" t="s">
-        <v>1413</v>
+        <v>17</v>
       </c>
       <c r="Q278" s="33" t="s">
         <v>13</v>
@@ -22222,19 +22180,19 @@
         <v>663</v>
       </c>
       <c r="B279" s="32" t="s">
-        <v>1293</v>
+        <v>1354</v>
       </c>
       <c r="C279" s="33" t="s">
-        <v>1294</v>
+        <v>802</v>
       </c>
       <c r="D279" s="32" t="s">
-        <v>638</v>
+        <v>653</v>
       </c>
       <c r="E279" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F279" s="34" t="s">
-        <v>763</v>
+        <v>1355</v>
       </c>
       <c r="G279" s="32" t="s">
         <v>13</v>
@@ -22264,7 +22222,7 @@
         <v>13</v>
       </c>
       <c r="P279" s="33" t="s">
-        <v>1413</v>
+        <v>17</v>
       </c>
       <c r="Q279" s="33" t="s">
         <v>13</v>
@@ -22284,7 +22242,7 @@
         <v>663</v>
       </c>
       <c r="B280" s="32" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="C280" s="33" t="s">
         <v>802</v>
@@ -22296,7 +22254,7 @@
         <v>13</v>
       </c>
       <c r="F280" s="34" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="G280" s="32" t="s">
         <v>13</v>
@@ -22346,7 +22304,7 @@
         <v>663</v>
       </c>
       <c r="B281" s="32" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="C281" s="33" t="s">
         <v>802</v>
@@ -22358,7 +22316,7 @@
         <v>13</v>
       </c>
       <c r="F281" s="34" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="G281" s="32" t="s">
         <v>13</v>
@@ -22408,7 +22366,7 @@
         <v>663</v>
       </c>
       <c r="B282" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="C282" s="33" t="s">
         <v>802</v>
@@ -22420,7 +22378,7 @@
         <v>13</v>
       </c>
       <c r="F282" s="34" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="G282" s="32" t="s">
         <v>13</v>
@@ -22470,7 +22428,7 @@
         <v>663</v>
       </c>
       <c r="B283" s="32" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="C283" s="33" t="s">
         <v>802</v>
@@ -22482,7 +22440,7 @@
         <v>13</v>
       </c>
       <c r="F283" s="34" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="G283" s="32" t="s">
         <v>13</v>
@@ -22491,7 +22449,7 @@
         <v>13</v>
       </c>
       <c r="I283" s="32" t="s">
-        <v>266</v>
+        <v>13</v>
       </c>
       <c r="J283" s="33" t="s">
         <v>13</v>
@@ -22503,7 +22461,7 @@
         <v>13</v>
       </c>
       <c r="M283" s="32" t="s">
-        <v>266</v>
+        <v>13</v>
       </c>
       <c r="N283" s="32" t="s">
         <v>13</v>
@@ -22532,7 +22490,7 @@
         <v>663</v>
       </c>
       <c r="B284" s="32" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="C284" s="33" t="s">
         <v>802</v>
@@ -22544,7 +22502,7 @@
         <v>13</v>
       </c>
       <c r="F284" s="34" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="G284" s="32" t="s">
         <v>13</v>
@@ -22594,7 +22552,7 @@
         <v>663</v>
       </c>
       <c r="B285" s="32" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="C285" s="33" t="s">
         <v>802</v>
@@ -22606,7 +22564,7 @@
         <v>13</v>
       </c>
       <c r="F285" s="34" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="G285" s="32" t="s">
         <v>13</v>
@@ -22615,7 +22573,7 @@
         <v>13</v>
       </c>
       <c r="I285" s="32" t="s">
-        <v>13</v>
+        <v>266</v>
       </c>
       <c r="J285" s="33" t="s">
         <v>13</v>
@@ -22627,7 +22585,7 @@
         <v>13</v>
       </c>
       <c r="M285" s="32" t="s">
-        <v>13</v>
+        <v>266</v>
       </c>
       <c r="N285" s="32" t="s">
         <v>13</v>
@@ -22656,7 +22614,7 @@
         <v>663</v>
       </c>
       <c r="B286" s="32" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="C286" s="33" t="s">
         <v>802</v>
@@ -22668,7 +22626,7 @@
         <v>13</v>
       </c>
       <c r="F286" s="34" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="G286" s="32" t="s">
         <v>13</v>
@@ -22718,7 +22676,7 @@
         <v>663</v>
       </c>
       <c r="B287" s="32" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="C287" s="33" t="s">
         <v>802</v>
@@ -22730,7 +22688,7 @@
         <v>13</v>
       </c>
       <c r="F287" s="34" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="G287" s="32" t="s">
         <v>13</v>
@@ -22780,7 +22738,7 @@
         <v>663</v>
       </c>
       <c r="B288" s="32" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
       <c r="C288" s="33" t="s">
         <v>802</v>
@@ -22792,7 +22750,7 @@
         <v>13</v>
       </c>
       <c r="F288" s="34" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="G288" s="32" t="s">
         <v>13</v>
@@ -22842,7 +22800,7 @@
         <v>663</v>
       </c>
       <c r="B289" s="32" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="C289" s="33" t="s">
         <v>802</v>
@@ -22854,7 +22812,7 @@
         <v>13</v>
       </c>
       <c r="F289" s="34" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="G289" s="32" t="s">
         <v>13</v>
@@ -22904,7 +22862,7 @@
         <v>663</v>
       </c>
       <c r="B290" s="32" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="C290" s="33" t="s">
         <v>802</v>
@@ -22916,7 +22874,7 @@
         <v>13</v>
       </c>
       <c r="F290" s="34" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="G290" s="32" t="s">
         <v>13</v>
@@ -22925,7 +22883,7 @@
         <v>13</v>
       </c>
       <c r="I290" s="32" t="s">
-        <v>266</v>
+        <v>13</v>
       </c>
       <c r="J290" s="33" t="s">
         <v>13</v>
@@ -22937,7 +22895,7 @@
         <v>13</v>
       </c>
       <c r="M290" s="32" t="s">
-        <v>266</v>
+        <v>13</v>
       </c>
       <c r="N290" s="32" t="s">
         <v>13</v>
@@ -22966,7 +22924,7 @@
         <v>663</v>
       </c>
       <c r="B291" s="32" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="C291" s="33" t="s">
         <v>802</v>
@@ -22978,7 +22936,7 @@
         <v>13</v>
       </c>
       <c r="F291" s="34" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="G291" s="32" t="s">
         <v>13</v>
@@ -23028,7 +22986,7 @@
         <v>663</v>
       </c>
       <c r="B292" s="32" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="C292" s="33" t="s">
         <v>802</v>
@@ -23040,7 +22998,7 @@
         <v>13</v>
       </c>
       <c r="F292" s="34" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="G292" s="32" t="s">
         <v>13</v>
@@ -23090,7 +23048,7 @@
         <v>663</v>
       </c>
       <c r="B293" s="32" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="C293" s="33" t="s">
         <v>802</v>
@@ -23102,7 +23060,7 @@
         <v>13</v>
       </c>
       <c r="F293" s="34" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="G293" s="32" t="s">
         <v>13</v>
@@ -23152,7 +23110,7 @@
         <v>663</v>
       </c>
       <c r="B294" s="32" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
       <c r="C294" s="33" t="s">
         <v>802</v>
@@ -23164,7 +23122,7 @@
         <v>13</v>
       </c>
       <c r="F294" s="34" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
       <c r="G294" s="32" t="s">
         <v>13</v>
@@ -23214,7 +23172,7 @@
         <v>663</v>
       </c>
       <c r="B295" s="32" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
       <c r="C295" s="33" t="s">
         <v>802</v>
@@ -23226,7 +23184,7 @@
         <v>13</v>
       </c>
       <c r="F295" s="34" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
       <c r="G295" s="32" t="s">
         <v>13</v>
@@ -23276,10 +23234,10 @@
         <v>663</v>
       </c>
       <c r="B296" s="32" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="C296" s="33" t="s">
-        <v>802</v>
+        <v>1389</v>
       </c>
       <c r="D296" s="32" t="s">
         <v>653</v>
@@ -23288,7 +23246,7 @@
         <v>13</v>
       </c>
       <c r="F296" s="34" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="G296" s="32" t="s">
         <v>13</v>
@@ -23297,7 +23255,7 @@
         <v>13</v>
       </c>
       <c r="I296" s="32" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J296" s="33" t="s">
         <v>13</v>
@@ -23309,7 +23267,7 @@
         <v>13</v>
       </c>
       <c r="M296" s="32" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N296" s="32" t="s">
         <v>13</v>
@@ -23318,7 +23276,7 @@
         <v>13</v>
       </c>
       <c r="P296" s="33" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q296" s="33" t="s">
         <v>13</v>
@@ -23338,19 +23296,19 @@
         <v>663</v>
       </c>
       <c r="B297" s="32" t="s">
-        <v>1394</v>
+        <v>683</v>
       </c>
       <c r="C297" s="33" t="s">
-        <v>802</v>
+        <v>684</v>
       </c>
       <c r="D297" s="32" t="s">
-        <v>653</v>
+        <v>66</v>
       </c>
       <c r="E297" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F297" s="34" t="s">
-        <v>1395</v>
+        <v>685</v>
       </c>
       <c r="G297" s="32" t="s">
         <v>13</v>
@@ -23359,7 +23317,7 @@
         <v>13</v>
       </c>
       <c r="I297" s="32" t="s">
-        <v>13</v>
+        <v>266</v>
       </c>
       <c r="J297" s="33" t="s">
         <v>13</v>
@@ -23371,7 +23329,7 @@
         <v>13</v>
       </c>
       <c r="M297" s="32" t="s">
-        <v>13</v>
+        <v>266</v>
       </c>
       <c r="N297" s="32" t="s">
         <v>13</v>
@@ -23397,19 +23355,19 @@
     </row>
     <row r="298" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="32" t="s">
-        <v>663</v>
+        <v>20</v>
       </c>
       <c r="B298" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="C298" s="33" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D298" s="32" t="s">
+        <v>637</v>
+      </c>
+      <c r="E298" s="33" t="s">
         <v>1396</v>
-      </c>
-      <c r="C298" s="33" t="s">
-        <v>802</v>
-      </c>
-      <c r="D298" s="32" t="s">
-        <v>653</v>
-      </c>
-      <c r="E298" s="33" t="s">
-        <v>13</v>
       </c>
       <c r="F298" s="34" t="s">
         <v>1397</v>
@@ -23421,10 +23379,10 @@
         <v>13</v>
       </c>
       <c r="I298" s="32" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J298" s="33" t="s">
-        <v>13</v>
+        <v>1041</v>
       </c>
       <c r="K298" s="32" t="s">
         <v>21</v>
@@ -23433,7 +23391,7 @@
         <v>13</v>
       </c>
       <c r="M298" s="32" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N298" s="32" t="s">
         <v>13</v>
@@ -23454,27 +23412,27 @@
         <v>13</v>
       </c>
       <c r="T298" s="32" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="299" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="32" t="s">
-        <v>663</v>
+        <v>20</v>
       </c>
       <c r="B299" s="32" t="s">
-        <v>1398</v>
+        <v>843</v>
       </c>
       <c r="C299" s="33" t="s">
-        <v>802</v>
+        <v>303</v>
       </c>
       <c r="D299" s="32" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E299" s="33" t="s">
-        <v>13</v>
+        <v>844</v>
       </c>
       <c r="F299" s="34" t="s">
-        <v>1399</v>
+        <v>842</v>
       </c>
       <c r="G299" s="32" t="s">
         <v>13</v>
@@ -23483,10 +23441,10 @@
         <v>13</v>
       </c>
       <c r="I299" s="32" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="J299" s="33" t="s">
-        <v>13</v>
+        <v>306</v>
       </c>
       <c r="K299" s="32" t="s">
         <v>21</v>
@@ -23495,7 +23453,7 @@
         <v>13</v>
       </c>
       <c r="M299" s="32" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="N299" s="32" t="s">
         <v>13</v>
@@ -23516,321 +23474,11 @@
         <v>13</v>
       </c>
       <c r="T299" s="32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="300" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A300" s="32" t="s">
-        <v>663</v>
-      </c>
-      <c r="B300" s="32" t="s">
-        <v>1400</v>
-      </c>
-      <c r="C300" s="33" t="s">
-        <v>802</v>
-      </c>
-      <c r="D300" s="32" t="s">
-        <v>653</v>
-      </c>
-      <c r="E300" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F300" s="34" t="s">
-        <v>1401</v>
-      </c>
-      <c r="G300" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H300" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="I300" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="J300" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="K300" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="L300" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="M300" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="N300" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="O300" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="P300" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q300" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="R300" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="S300" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="T300" s="32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="301" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A301" s="32" t="s">
-        <v>663</v>
-      </c>
-      <c r="B301" s="32" t="s">
-        <v>1402</v>
-      </c>
-      <c r="C301" s="33" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D301" s="32" t="s">
-        <v>653</v>
-      </c>
-      <c r="E301" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F301" s="34" t="s">
-        <v>1404</v>
-      </c>
-      <c r="G301" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H301" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="I301" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="J301" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="K301" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="L301" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="M301" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="N301" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="O301" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="P301" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q301" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="R301" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="S301" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="T301" s="32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="302" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A302" s="32" t="s">
-        <v>663</v>
-      </c>
-      <c r="B302" s="32" t="s">
-        <v>683</v>
-      </c>
-      <c r="C302" s="33" t="s">
-        <v>684</v>
-      </c>
-      <c r="D302" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="E302" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F302" s="34" t="s">
-        <v>685</v>
-      </c>
-      <c r="G302" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H302" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="I302" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="J302" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="K302" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="L302" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="M302" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="N302" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="O302" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="P302" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q302" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="R302" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="S302" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="T302" s="32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="303" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A303" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="B303" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="C303" s="33" t="s">
-        <v>1052</v>
-      </c>
-      <c r="D303" s="32" t="s">
-        <v>637</v>
-      </c>
-      <c r="E303" s="33" t="s">
-        <v>1410</v>
-      </c>
-      <c r="F303" s="34" t="s">
-        <v>1411</v>
-      </c>
-      <c r="G303" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H303" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="I303" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="J303" s="33" t="s">
-        <v>1055</v>
-      </c>
-      <c r="K303" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="L303" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="M303" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="N303" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="O303" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="P303" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q303" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="R303" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="S303" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="T303" s="32" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="304" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A304" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="B304" s="32" t="s">
-        <v>843</v>
-      </c>
-      <c r="C304" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="D304" s="32" t="s">
-        <v>651</v>
-      </c>
-      <c r="E304" s="33" t="s">
-        <v>844</v>
-      </c>
-      <c r="F304" s="34" t="s">
-        <v>842</v>
-      </c>
-      <c r="G304" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H304" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="I304" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J304" s="33" t="s">
-        <v>306</v>
-      </c>
-      <c r="K304" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="L304" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="M304" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="N304" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="O304" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="P304" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q304" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="R304" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="S304" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="T304" s="32" t="s">
-        <v>30</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:T304" xr:uid="{6EBD8DE6-E0AD-4EC4-ABEF-FC9321AB7545}"/>
+  <autoFilter ref="A1:T299" xr:uid="{6EBD8DE6-E0AD-4EC4-ABEF-FC9321AB7545}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
